--- a/research/traditional_assets/database/data/malaysia/malaysia_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_homebuilding.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1030536802794581</v>
+        <v>0.1028405514467874</v>
       </c>
       <c r="C2">
-        <v>21.98590118619236</v>
+        <v>21.80143694035028</v>
       </c>
       <c r="D2">
-        <v>17.58590118619237</v>
+        <v>17.62203694035028</v>
       </c>
       <c r="E2">
-        <v>-1.46</v>
+        <v>-1.2394</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2206</v>
       </c>
       <c r="G2">
         <v>4.4</v>
@@ -1564,28 +1564,28 @@
         <v>2.94</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01109618</v>
       </c>
       <c r="N2">
-        <v>2.94</v>
+        <v>2.92890382</v>
       </c>
       <c r="O2">
-        <v>0.7056</v>
+        <v>0.7029369167999999</v>
       </c>
       <c r="P2">
-        <v>2.2344</v>
+        <v>2.2259669032</v>
       </c>
       <c r="Q2">
-        <v>2.4744</v>
+        <v>2.4659669032</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1030536802794581</v>
+        <v>0.1034932034816034</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.9727902940026416</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>264.956047937218</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1028405514467874</v>
+        <v>0.1026274226141167</v>
       </c>
       <c r="C3">
-        <v>21.80143694035028</v>
+        <v>21.61712150478531</v>
       </c>
       <c r="D3">
-        <v>17.62203694035028</v>
+        <v>17.65832150478531</v>
       </c>
       <c r="E3">
-        <v>-1.2394</v>
+        <v>-1.0188</v>
       </c>
       <c r="F3">
-        <v>0.2206</v>
+        <v>0.4412</v>
       </c>
       <c r="G3">
         <v>4.4</v>
@@ -1646,28 +1646,28 @@
         <v>2.94</v>
       </c>
       <c r="M3">
-        <v>0.01109618</v>
+        <v>0.02219236</v>
       </c>
       <c r="N3">
-        <v>2.92890382</v>
+        <v>2.91780764</v>
       </c>
       <c r="O3">
-        <v>0.7029369167999999</v>
+        <v>0.7002738336</v>
       </c>
       <c r="P3">
-        <v>2.2259669032</v>
+        <v>2.2175338064</v>
       </c>
       <c r="Q3">
-        <v>2.4659669032</v>
+        <v>2.4575338064</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1034932034816034</v>
+        <v>0.103941696545017</v>
       </c>
       <c r="T3">
-        <v>0.9727902940026416</v>
+        <v>0.9803525313666213</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>264.956047937218</v>
+        <v>132.478023968609</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1026274226141167</v>
+        <v>0.102414293781446</v>
       </c>
       <c r="C4">
-        <v>21.61712150478531</v>
+        <v>21.43295580061517</v>
       </c>
       <c r="D4">
-        <v>17.65832150478531</v>
+        <v>17.69475580061517</v>
       </c>
       <c r="E4">
-        <v>-1.0188</v>
+        <v>-0.7981999999999999</v>
       </c>
       <c r="F4">
-        <v>0.4412</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="G4">
         <v>4.4</v>
@@ -1728,28 +1728,28 @@
         <v>2.94</v>
       </c>
       <c r="M4">
-        <v>0.02219236</v>
+        <v>0.03328854</v>
       </c>
       <c r="N4">
-        <v>2.91780764</v>
+        <v>2.90671146</v>
       </c>
       <c r="O4">
-        <v>0.7002738336</v>
+        <v>0.6976107504</v>
       </c>
       <c r="P4">
-        <v>2.2175338064</v>
+        <v>2.2091007096</v>
       </c>
       <c r="Q4">
-        <v>2.4575338064</v>
+        <v>2.4491007096</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.103941696545017</v>
+        <v>0.1043994368880887</v>
       </c>
       <c r="T4">
-        <v>0.9803525313666213</v>
+        <v>0.9880706911504771</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>132.478023968609</v>
+        <v>88.31868264573934</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.102414293781446</v>
+        <v>0.1022011649487753</v>
       </c>
       <c r="C5">
-        <v>21.43295580061517</v>
+        <v>21.24894075657545</v>
       </c>
       <c r="D5">
-        <v>17.69475580061517</v>
+        <v>17.73134075657546</v>
       </c>
       <c r="E5">
-        <v>-0.7981999999999999</v>
+        <v>-0.5775999999999999</v>
       </c>
       <c r="F5">
-        <v>0.6618000000000001</v>
+        <v>0.8824000000000001</v>
       </c>
       <c r="G5">
         <v>4.4</v>
@@ -1810,28 +1810,28 @@
         <v>2.94</v>
       </c>
       <c r="M5">
-        <v>0.03328854</v>
+        <v>0.04438472</v>
       </c>
       <c r="N5">
-        <v>2.90671146</v>
+        <v>2.89561528</v>
       </c>
       <c r="O5">
-        <v>0.6976107504</v>
+        <v>0.6949476671999999</v>
       </c>
       <c r="P5">
-        <v>2.2091007096</v>
+        <v>2.2006676128</v>
       </c>
       <c r="Q5">
-        <v>2.4491007096</v>
+        <v>2.4406676128</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1043994368880887</v>
+        <v>0.1048667134883076</v>
       </c>
       <c r="T5">
-        <v>0.9880706911504771</v>
+        <v>0.9959496459298296</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.31868264573934</v>
+        <v>66.2390119843045</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1022011649487753</v>
+        <v>0.1019880361161046</v>
       </c>
       <c r="C6">
-        <v>21.24894075657545</v>
+        <v>21.06507730909853</v>
       </c>
       <c r="D6">
-        <v>17.73134075657546</v>
+        <v>17.76807730909853</v>
       </c>
       <c r="E6">
-        <v>-0.5775999999999999</v>
+        <v>-0.3569999999999998</v>
       </c>
       <c r="F6">
-        <v>0.8824000000000001</v>
+        <v>1.103</v>
       </c>
       <c r="G6">
         <v>4.4</v>
@@ -1892,28 +1892,28 @@
         <v>2.94</v>
       </c>
       <c r="M6">
-        <v>0.04438472</v>
+        <v>0.05548090000000001</v>
       </c>
       <c r="N6">
-        <v>2.89561528</v>
+        <v>2.8845191</v>
       </c>
       <c r="O6">
-        <v>0.6949476671999999</v>
+        <v>0.6922845839999999</v>
       </c>
       <c r="P6">
-        <v>2.2006676128</v>
+        <v>2.192234516</v>
       </c>
       <c r="Q6">
-        <v>2.4406676128</v>
+        <v>2.432234516</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1048667134883076</v>
+        <v>0.1053438274906364</v>
       </c>
       <c r="T6">
-        <v>0.9959496459298296</v>
+        <v>1.003994473441379</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.2390119843045</v>
+        <v>52.9912095874436</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1019880361161046</v>
+        <v>0.1017749072834339</v>
       </c>
       <c r="C7">
-        <v>21.06507730909853</v>
+        <v>20.88136640239344</v>
       </c>
       <c r="D7">
-        <v>17.76807730909853</v>
+        <v>17.80496640239344</v>
       </c>
       <c r="E7">
-        <v>-0.3569999999999998</v>
+        <v>-0.1363999999999996</v>
       </c>
       <c r="F7">
-        <v>1.103</v>
+        <v>1.3236</v>
       </c>
       <c r="G7">
         <v>4.4</v>
@@ -1974,28 +1974,28 @@
         <v>2.94</v>
       </c>
       <c r="M7">
-        <v>0.05548090000000001</v>
+        <v>0.06657708000000001</v>
       </c>
       <c r="N7">
-        <v>2.8845191</v>
+        <v>2.87342292</v>
       </c>
       <c r="O7">
-        <v>0.6922845839999999</v>
+        <v>0.6896215008</v>
       </c>
       <c r="P7">
-        <v>2.192234516</v>
+        <v>2.1838014192</v>
       </c>
       <c r="Q7">
-        <v>2.432234516</v>
+        <v>2.4238014192</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1053438274906364</v>
+        <v>0.1058310928547169</v>
       </c>
       <c r="T7">
-        <v>1.003994473441379</v>
+        <v>1.012210467495728</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.9912095874436</v>
+        <v>44.15934132286966</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1017749072834339</v>
+        <v>0.1015617784507632</v>
       </c>
       <c r="C8">
-        <v>20.88136640239344</v>
+        <v>20.69780898852679</v>
       </c>
       <c r="D8">
-        <v>17.80496640239344</v>
+        <v>17.84200898852679</v>
       </c>
       <c r="E8">
-        <v>-0.1363999999999999</v>
+        <v>0.08420000000000005</v>
       </c>
       <c r="F8">
-        <v>1.3236</v>
+        <v>1.5442</v>
       </c>
       <c r="G8">
         <v>4.4</v>
@@ -2056,28 +2056,28 @@
         <v>2.94</v>
       </c>
       <c r="M8">
-        <v>0.06657708</v>
+        <v>0.07767325999999999</v>
       </c>
       <c r="N8">
-        <v>2.87342292</v>
+        <v>2.86232674</v>
       </c>
       <c r="O8">
-        <v>0.6896215008</v>
+        <v>0.6869584176</v>
       </c>
       <c r="P8">
-        <v>2.1838014192</v>
+        <v>2.1753683224</v>
       </c>
       <c r="Q8">
-        <v>2.4238014192</v>
+        <v>2.4153683224</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1058310928547169</v>
+        <v>0.1063288370438314</v>
       </c>
       <c r="T8">
-        <v>1.012210467495728</v>
+        <v>1.020603149594255</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.15934132286967</v>
+        <v>37.85086399103115</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1015617784507632</v>
+        <v>0.1013486496180925</v>
       </c>
       <c r="C9">
-        <v>20.69780898852679</v>
+        <v>20.51440602750468</v>
       </c>
       <c r="D9">
-        <v>17.84200898852679</v>
+        <v>17.87920602750468</v>
       </c>
       <c r="E9">
-        <v>0.08420000000000027</v>
+        <v>0.3048000000000002</v>
       </c>
       <c r="F9">
-        <v>1.5442</v>
+        <v>1.7648</v>
       </c>
       <c r="G9">
         <v>4.4</v>
@@ -2138,28 +2138,28 @@
         <v>2.94</v>
       </c>
       <c r="M9">
-        <v>0.07767326000000001</v>
+        <v>0.08876944000000001</v>
       </c>
       <c r="N9">
-        <v>2.86232674</v>
+        <v>2.85123056</v>
       </c>
       <c r="O9">
-        <v>0.6869584176</v>
+        <v>0.6842953343999999</v>
       </c>
       <c r="P9">
-        <v>2.1753683224</v>
+        <v>2.1669352256</v>
       </c>
       <c r="Q9">
-        <v>2.4153683224</v>
+        <v>2.4069352256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1063288370438314</v>
+        <v>0.1068374017587962</v>
       </c>
       <c r="T9">
-        <v>1.020603149594255</v>
+        <v>1.029178281303621</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.85086399103114</v>
+        <v>33.11950599215225</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1013486496180925</v>
+        <v>0.1011355207854218</v>
       </c>
       <c r="C10">
-        <v>20.51440602750468</v>
+        <v>20.33115848735561</v>
       </c>
       <c r="D10">
-        <v>17.87920602750468</v>
+        <v>17.9165584873556</v>
       </c>
       <c r="E10">
-        <v>0.3048000000000002</v>
+        <v>0.5254000000000001</v>
       </c>
       <c r="F10">
-        <v>1.7648</v>
+        <v>1.9854</v>
       </c>
       <c r="G10">
         <v>4.4</v>
@@ -2220,28 +2220,28 @@
         <v>2.94</v>
       </c>
       <c r="M10">
-        <v>0.08876944000000001</v>
+        <v>0.09986562</v>
       </c>
       <c r="N10">
-        <v>2.85123056</v>
+        <v>2.84013438</v>
       </c>
       <c r="O10">
-        <v>0.6842953343999999</v>
+        <v>0.6816322511999999</v>
       </c>
       <c r="P10">
-        <v>2.1669352256</v>
+        <v>2.1585021288</v>
       </c>
       <c r="Q10">
-        <v>2.4069352256</v>
+        <v>2.3985021288</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1068374017587962</v>
+        <v>0.1073571437202437</v>
       </c>
       <c r="T10">
-        <v>1.029178281303621</v>
+        <v>1.037941877446159</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.11950599215225</v>
+        <v>29.43956088191311</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1011355207854218</v>
+        <v>0.1009223919527511</v>
       </c>
       <c r="C11">
-        <v>20.33115848735561</v>
+        <v>20.14806734421446</v>
       </c>
       <c r="D11">
-        <v>17.9165584873556</v>
+        <v>17.95406734421446</v>
       </c>
       <c r="E11">
-        <v>0.5254000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="F11">
-        <v>1.9854</v>
+        <v>2.206</v>
       </c>
       <c r="G11">
         <v>4.4</v>
@@ -2302,28 +2302,28 @@
         <v>2.94</v>
       </c>
       <c r="M11">
-        <v>0.09986562</v>
+        <v>0.1109618</v>
       </c>
       <c r="N11">
-        <v>2.84013438</v>
+        <v>2.8290382</v>
       </c>
       <c r="O11">
-        <v>0.6816322511999999</v>
+        <v>0.678969168</v>
       </c>
       <c r="P11">
-        <v>2.1585021288</v>
+        <v>2.150069032</v>
       </c>
       <c r="Q11">
-        <v>2.3985021288</v>
+        <v>2.390069032</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1073571437202437</v>
+        <v>0.1078884355030568</v>
       </c>
       <c r="T11">
-        <v>1.037941877446159</v>
+        <v>1.046900220169643</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.43956088191311</v>
+        <v>26.4956047937218</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1009223919527511</v>
+        <v>0.1007092631200804</v>
       </c>
       <c r="C12">
-        <v>20.14806734421446</v>
+        <v>19.96513358240754</v>
       </c>
       <c r="D12">
-        <v>17.95406734421446</v>
+        <v>17.99173358240754</v>
       </c>
       <c r="E12">
-        <v>0.7460000000000004</v>
+        <v>0.9666000000000001</v>
       </c>
       <c r="F12">
-        <v>2.206</v>
+        <v>2.4266</v>
       </c>
       <c r="G12">
         <v>4.4</v>
@@ -2384,28 +2384,28 @@
         <v>2.94</v>
       </c>
       <c r="M12">
-        <v>0.1109618</v>
+        <v>0.12205798</v>
       </c>
       <c r="N12">
-        <v>2.8290382</v>
+        <v>2.81794202</v>
       </c>
       <c r="O12">
-        <v>0.678969168</v>
+        <v>0.6763060848</v>
       </c>
       <c r="P12">
-        <v>2.150069032</v>
+        <v>2.1416359352</v>
       </c>
       <c r="Q12">
-        <v>2.390069032</v>
+        <v>2.3816359352</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1078884355030568</v>
+        <v>0.1084316664270566</v>
       </c>
       <c r="T12">
-        <v>1.046900220169643</v>
+        <v>1.056059873965565</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.4956047937218</v>
+        <v>24.086913448838</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1007092631200804</v>
+        <v>0.1004961342874097</v>
       </c>
       <c r="C13">
-        <v>19.96513358240754</v>
+        <v>19.7823581945387</v>
       </c>
       <c r="D13">
-        <v>17.99173358240754</v>
+        <v>18.0295581945387</v>
       </c>
       <c r="E13">
-        <v>0.9666000000000001</v>
+        <v>1.1872</v>
       </c>
       <c r="F13">
-        <v>2.4266</v>
+        <v>2.6472</v>
       </c>
       <c r="G13">
         <v>4.4</v>
@@ -2466,28 +2466,28 @@
         <v>2.94</v>
       </c>
       <c r="M13">
-        <v>0.12205798</v>
+        <v>0.13315416</v>
       </c>
       <c r="N13">
-        <v>2.81794202</v>
+        <v>2.80684584</v>
       </c>
       <c r="O13">
-        <v>0.6763060848</v>
+        <v>0.6736430015999999</v>
       </c>
       <c r="P13">
-        <v>2.1416359352</v>
+        <v>2.1332028384</v>
       </c>
       <c r="Q13">
-        <v>2.3816359352</v>
+        <v>2.3732028384</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1084316664270566</v>
+        <v>0.1089872435084201</v>
       </c>
       <c r="T13">
-        <v>1.056059873965565</v>
+        <v>1.065427701711393</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.086913448838</v>
+        <v>22.07967066143484</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1004961342874097</v>
+        <v>0.100283005454739</v>
       </c>
       <c r="C14">
-        <v>19.7823581945387</v>
+        <v>19.59974218157649</v>
       </c>
       <c r="D14">
-        <v>18.0295581945387</v>
+        <v>18.06754218157649</v>
       </c>
       <c r="E14">
-        <v>1.1872</v>
+        <v>1.4078</v>
       </c>
       <c r="F14">
-        <v>2.6472</v>
+        <v>2.8678</v>
       </c>
       <c r="G14">
         <v>4.4</v>
@@ -2548,28 +2548,28 @@
         <v>2.94</v>
       </c>
       <c r="M14">
-        <v>0.13315416</v>
+        <v>0.14425034</v>
       </c>
       <c r="N14">
-        <v>2.80684584</v>
+        <v>2.79574966</v>
       </c>
       <c r="O14">
-        <v>0.6736430015999999</v>
+        <v>0.6709799183999999</v>
       </c>
       <c r="P14">
-        <v>2.1332028384</v>
+        <v>2.1247697416</v>
       </c>
       <c r="Q14">
-        <v>2.3732028384</v>
+        <v>2.3647697416</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1089872435084201</v>
+        <v>0.1095555924767115</v>
       </c>
       <c r="T14">
-        <v>1.065427701711393</v>
+        <v>1.075010881819195</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.07967066143484</v>
+        <v>20.38123445670908</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.100283005454739</v>
+        <v>0.1000698766220683</v>
       </c>
       <c r="C15">
-        <v>19.59974218157649</v>
+        <v>19.41728655294248</v>
       </c>
       <c r="D15">
-        <v>18.06754218157649</v>
+        <v>18.10568655294248</v>
       </c>
       <c r="E15">
-        <v>1.4078</v>
+        <v>1.628400000000001</v>
       </c>
       <c r="F15">
-        <v>2.8678</v>
+        <v>3.0884</v>
       </c>
       <c r="G15">
         <v>4.4</v>
@@ -2630,28 +2630,28 @@
         <v>2.94</v>
       </c>
       <c r="M15">
-        <v>0.14425034</v>
+        <v>0.15534652</v>
       </c>
       <c r="N15">
-        <v>2.79574966</v>
+        <v>2.78465348</v>
       </c>
       <c r="O15">
-        <v>0.6709799183999999</v>
+        <v>0.6683168352</v>
       </c>
       <c r="P15">
-        <v>2.1247697416</v>
+        <v>2.1163366448</v>
       </c>
       <c r="Q15">
-        <v>2.3647697416</v>
+        <v>2.3563366448</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1095555924767115</v>
+        <v>0.1101371588628701</v>
       </c>
       <c r="T15">
-        <v>1.075010881819195</v>
+        <v>1.084816926580667</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.38123445670908</v>
+        <v>18.92543199551557</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1000698766220683</v>
+        <v>0.09985674778939763</v>
       </c>
       <c r="C16">
-        <v>19.41728655294248</v>
+        <v>19.23499232660067</v>
       </c>
       <c r="D16">
-        <v>18.10568655294248</v>
+        <v>18.14399232660067</v>
       </c>
       <c r="E16">
-        <v>1.628400000000001</v>
+        <v>1.849000000000001</v>
       </c>
       <c r="F16">
-        <v>3.0884</v>
+        <v>3.309000000000001</v>
       </c>
       <c r="G16">
         <v>4.4</v>
@@ -2712,28 +2712,28 @@
         <v>2.94</v>
       </c>
       <c r="M16">
-        <v>0.15534652</v>
+        <v>0.1664427000000001</v>
       </c>
       <c r="N16">
-        <v>2.78465348</v>
+        <v>2.7735573</v>
       </c>
       <c r="O16">
-        <v>0.6683168352</v>
+        <v>0.6656537519999999</v>
       </c>
       <c r="P16">
-        <v>2.1163366448</v>
+        <v>2.107903548</v>
       </c>
       <c r="Q16">
-        <v>2.3563366448</v>
+        <v>2.347903548</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1101371588628701</v>
+        <v>0.1107324091639972</v>
       </c>
       <c r="T16">
-        <v>1.084816926580667</v>
+        <v>1.094853701807115</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.92543199551557</v>
+        <v>17.66373652914786</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0998567477893976</v>
+        <v>0.09964361895672691</v>
       </c>
       <c r="C17">
-        <v>19.23499232660068</v>
+        <v>19.0528605291481</v>
       </c>
       <c r="D17">
-        <v>18.14399232660068</v>
+        <v>18.1824605291481</v>
       </c>
       <c r="E17">
-        <v>1.849</v>
+        <v>2.0696</v>
       </c>
       <c r="F17">
-        <v>3.309</v>
+        <v>3.5296</v>
       </c>
       <c r="G17">
         <v>4.4</v>
@@ -2794,28 +2794,28 @@
         <v>2.94</v>
       </c>
       <c r="M17">
-        <v>0.1664427</v>
+        <v>0.17753888</v>
       </c>
       <c r="N17">
-        <v>2.7735573</v>
+        <v>2.76246112</v>
       </c>
       <c r="O17">
-        <v>0.6656537519999999</v>
+        <v>0.6629906687999999</v>
       </c>
       <c r="P17">
-        <v>2.107903548</v>
+        <v>2.0994704512</v>
       </c>
       <c r="Q17">
-        <v>2.347903548</v>
+        <v>2.3394704512</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1107324091639972</v>
+        <v>0.1113418320913416</v>
       </c>
       <c r="T17">
-        <v>1.094853701807115</v>
+        <v>1.105129447872287</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.66373652914787</v>
+        <v>16.55975299607612</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09964361895672691</v>
+        <v>0.09943049012405621</v>
       </c>
       <c r="C18">
-        <v>19.0528605291481</v>
+        <v>18.87089219590646</v>
       </c>
       <c r="D18">
-        <v>18.1824605291481</v>
+        <v>18.22109219590646</v>
       </c>
       <c r="E18">
-        <v>2.0696</v>
+        <v>2.290200000000001</v>
       </c>
       <c r="F18">
-        <v>3.5296</v>
+        <v>3.750200000000001</v>
       </c>
       <c r="G18">
         <v>4.4</v>
@@ -2876,28 +2876,28 @@
         <v>2.94</v>
       </c>
       <c r="M18">
-        <v>0.17753888</v>
+        <v>0.18863506</v>
       </c>
       <c r="N18">
-        <v>2.76246112</v>
+        <v>2.75136494</v>
       </c>
       <c r="O18">
-        <v>0.6629906687999999</v>
+        <v>0.6603275855999999</v>
       </c>
       <c r="P18">
-        <v>2.0994704512</v>
+        <v>2.0910373544</v>
       </c>
       <c r="Q18">
-        <v>2.3394704512</v>
+        <v>2.3310373544</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1113418320913416</v>
+        <v>0.1119659399085015</v>
       </c>
       <c r="T18">
-        <v>1.105129447872287</v>
+        <v>1.11565280227638</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.55975299607612</v>
+        <v>15.58564987865988</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09943049012405621</v>
+        <v>0.09921736129138553</v>
       </c>
       <c r="C19">
-        <v>18.87089219590646</v>
+        <v>18.68908837101504</v>
       </c>
       <c r="D19">
-        <v>18.22109219590646</v>
+        <v>18.25988837101504</v>
       </c>
       <c r="E19">
-        <v>2.290200000000001</v>
+        <v>2.510800000000001</v>
       </c>
       <c r="F19">
-        <v>3.750200000000001</v>
+        <v>3.970800000000001</v>
       </c>
       <c r="G19">
         <v>4.4</v>
@@ -2958,28 +2958,28 @@
         <v>2.94</v>
       </c>
       <c r="M19">
-        <v>0.18863506</v>
+        <v>0.19973124</v>
       </c>
       <c r="N19">
-        <v>2.75136494</v>
+        <v>2.74026876</v>
       </c>
       <c r="O19">
-        <v>0.6603275855999999</v>
+        <v>0.6576645024</v>
       </c>
       <c r="P19">
-        <v>2.0910373544</v>
+        <v>2.0826042576</v>
       </c>
       <c r="Q19">
-        <v>2.3310373544</v>
+        <v>2.3226042576</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1119659399085015</v>
+        <v>0.1126052698675433</v>
       </c>
       <c r="T19">
-        <v>1.11565280227638</v>
+        <v>1.12643282386106</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.58564987865988</v>
+        <v>14.71978044095655</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09921736129138552</v>
+        <v>0.09900423245871483</v>
       </c>
       <c r="C20">
-        <v>18.68908837101504</v>
+        <v>18.50745010752483</v>
       </c>
       <c r="D20">
-        <v>18.25988837101504</v>
+        <v>18.29885010752482</v>
       </c>
       <c r="E20">
-        <v>2.5108</v>
+        <v>2.731400000000001</v>
       </c>
       <c r="F20">
-        <v>3.9708</v>
+        <v>4.191400000000001</v>
       </c>
       <c r="G20">
         <v>4.4</v>
@@ -3040,28 +3040,28 @@
         <v>2.94</v>
       </c>
       <c r="M20">
-        <v>0.19973124</v>
+        <v>0.21082742</v>
       </c>
       <c r="N20">
-        <v>2.74026876</v>
+        <v>2.72917258</v>
       </c>
       <c r="O20">
-        <v>0.6576645024</v>
+        <v>0.6550014191999999</v>
       </c>
       <c r="P20">
-        <v>2.0826042576</v>
+        <v>2.0741711608</v>
       </c>
       <c r="Q20">
-        <v>2.3226042576</v>
+        <v>2.3141711608</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1126052698675433</v>
+        <v>0.1132603857514998</v>
       </c>
       <c r="T20">
-        <v>1.126432823861059</v>
+        <v>1.1374790188182</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.71978044095656</v>
+        <v>13.94505515459042</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09900423245871483</v>
+        <v>0.09879110362604411</v>
       </c>
       <c r="C21">
-        <v>18.50745010752483</v>
+        <v>18.32597846749371</v>
       </c>
       <c r="D21">
-        <v>18.29885010752482</v>
+        <v>18.33797846749371</v>
       </c>
       <c r="E21">
-        <v>2.731400000000001</v>
+        <v>2.952000000000001</v>
       </c>
       <c r="F21">
-        <v>4.191400000000001</v>
+        <v>4.412000000000001</v>
       </c>
       <c r="G21">
         <v>4.4</v>
@@ -3122,28 +3122,28 @@
         <v>2.94</v>
       </c>
       <c r="M21">
-        <v>0.21082742</v>
+        <v>0.2219236</v>
       </c>
       <c r="N21">
-        <v>2.72917258</v>
+        <v>2.7180764</v>
       </c>
       <c r="O21">
-        <v>0.6550014191999999</v>
+        <v>0.6523383359999999</v>
       </c>
       <c r="P21">
-        <v>2.0741711608</v>
+        <v>2.065738064</v>
       </c>
       <c r="Q21">
-        <v>2.3141711608</v>
+        <v>2.305738064</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1132603857514998</v>
+        <v>0.1139318795325551</v>
       </c>
       <c r="T21">
-        <v>1.1374790188182</v>
+        <v>1.14880136864927</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.94505515459042</v>
+        <v>13.2478023968609</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09879110362604411</v>
+        <v>0.09881737479337342</v>
       </c>
       <c r="C22">
-        <v>18.32597846749371</v>
+        <v>18.10054629961622</v>
       </c>
       <c r="D22">
-        <v>18.33797846749371</v>
+        <v>18.33314629961622</v>
       </c>
       <c r="E22">
-        <v>2.952000000000001</v>
+        <v>3.172600000000001</v>
       </c>
       <c r="F22">
-        <v>4.412000000000001</v>
+        <v>4.632600000000001</v>
       </c>
       <c r="G22">
         <v>4.4</v>
@@ -3204,45 +3204,45 @@
         <v>2.94</v>
       </c>
       <c r="M22">
-        <v>0.2219236</v>
+        <v>0.23996868</v>
       </c>
       <c r="N22">
-        <v>2.7180764</v>
+        <v>2.70003132</v>
       </c>
       <c r="O22">
-        <v>0.6523383359999999</v>
+        <v>0.6480075167999999</v>
       </c>
       <c r="P22">
-        <v>2.065738064</v>
+        <v>2.0520238032</v>
       </c>
       <c r="Q22">
-        <v>2.305738064</v>
+        <v>2.2920238032</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1139318795325551</v>
+        <v>0.1146203731561689</v>
       </c>
       <c r="T22">
-        <v>1.14880136864927</v>
+        <v>1.160410360248215</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.2478023968609</v>
+        <v>12.25159883364779</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09881737479337342</v>
+        <v>0.09861564596070271</v>
       </c>
       <c r="C23">
-        <v>18.10054629961622</v>
+        <v>17.9171165769088</v>
       </c>
       <c r="D23">
-        <v>18.33314629961622</v>
+        <v>18.3703165769088</v>
       </c>
       <c r="E23">
-        <v>3.1726</v>
+        <v>3.3932</v>
       </c>
       <c r="F23">
-        <v>4.6326</v>
+        <v>4.8532</v>
       </c>
       <c r="G23">
         <v>4.4</v>
@@ -3286,28 +3286,28 @@
         <v>2.94</v>
       </c>
       <c r="M23">
-        <v>0.23996868</v>
+        <v>0.25139576</v>
       </c>
       <c r="N23">
-        <v>2.70003132</v>
+        <v>2.68860424</v>
       </c>
       <c r="O23">
-        <v>0.6480075167999999</v>
+        <v>0.6452650176</v>
       </c>
       <c r="P23">
-        <v>2.0520238032</v>
+        <v>2.0433392224</v>
       </c>
       <c r="Q23">
-        <v>2.2920238032</v>
+        <v>2.2833392224</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1146203731561689</v>
+        <v>0.1153265204624394</v>
       </c>
       <c r="T23">
-        <v>1.160410360248215</v>
+        <v>1.172317018298415</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.25159883364779</v>
+        <v>11.69470797757289</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09861564596070271</v>
+        <v>0.09841391712803203</v>
       </c>
       <c r="C24">
-        <v>17.9171165769088</v>
+        <v>17.73383788517259</v>
       </c>
       <c r="D24">
-        <v>18.3703165769088</v>
+        <v>18.40763788517259</v>
       </c>
       <c r="E24">
-        <v>3.3932</v>
+        <v>3.6138</v>
       </c>
       <c r="F24">
-        <v>4.8532</v>
+        <v>5.0738</v>
       </c>
       <c r="G24">
         <v>4.4</v>
@@ -3368,28 +3368,28 @@
         <v>2.94</v>
       </c>
       <c r="M24">
-        <v>0.25139576</v>
+        <v>0.26282284</v>
       </c>
       <c r="N24">
-        <v>2.68860424</v>
+        <v>2.67717716</v>
       </c>
       <c r="O24">
-        <v>0.6452650176</v>
+        <v>0.6425225184</v>
       </c>
       <c r="P24">
-        <v>2.0433392224</v>
+        <v>2.0346546416</v>
       </c>
       <c r="Q24">
-        <v>2.2833392224</v>
+        <v>2.2746546416</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1153265204624394</v>
+        <v>0.1160510092571845</v>
       </c>
       <c r="T24">
-        <v>1.172317018298415</v>
+        <v>1.184532940194075</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.69470797757289</v>
+        <v>11.18624241333059</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09841391712803203</v>
+        <v>0.09821218829536131</v>
       </c>
       <c r="C25">
-        <v>17.73383788517259</v>
+        <v>17.55071114678936</v>
       </c>
       <c r="D25">
-        <v>18.40763788517259</v>
+        <v>18.44511114678936</v>
       </c>
       <c r="E25">
-        <v>3.6138</v>
+        <v>3.834400000000001</v>
       </c>
       <c r="F25">
-        <v>5.0738</v>
+        <v>5.294400000000001</v>
       </c>
       <c r="G25">
         <v>4.4</v>
@@ -3450,28 +3450,28 @@
         <v>2.94</v>
       </c>
       <c r="M25">
-        <v>0.26282284</v>
+        <v>0.27424992</v>
       </c>
       <c r="N25">
-        <v>2.67717716</v>
+        <v>2.66575008</v>
       </c>
       <c r="O25">
-        <v>0.6425225184</v>
+        <v>0.6397800191999999</v>
       </c>
       <c r="P25">
-        <v>2.0346546416</v>
+        <v>2.0259700608</v>
       </c>
       <c r="Q25">
-        <v>2.2746546416</v>
+        <v>2.2659700608</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1160510092571845</v>
+        <v>0.116794563546528</v>
       </c>
       <c r="T25">
-        <v>1.184532940194075</v>
+        <v>1.197070333718567</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.18624241333059</v>
+        <v>10.72014897944182</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09821218829536131</v>
+        <v>0.09801045946269062</v>
       </c>
       <c r="C26">
-        <v>17.55071114678936</v>
+        <v>17.3677372916671</v>
       </c>
       <c r="D26">
-        <v>18.44511114678936</v>
+        <v>18.48273729166711</v>
       </c>
       <c r="E26">
-        <v>3.8344</v>
+        <v>4.055000000000001</v>
       </c>
       <c r="F26">
-        <v>5.2944</v>
+        <v>5.515000000000001</v>
       </c>
       <c r="G26">
         <v>4.4</v>
@@ -3532,28 +3532,28 @@
         <v>2.94</v>
       </c>
       <c r="M26">
-        <v>0.27424992</v>
+        <v>0.285677</v>
       </c>
       <c r="N26">
-        <v>2.66575008</v>
+        <v>2.654323</v>
       </c>
       <c r="O26">
-        <v>0.6397800191999999</v>
+        <v>0.6370375199999999</v>
       </c>
       <c r="P26">
-        <v>2.0259700608</v>
+        <v>2.01728548</v>
       </c>
       <c r="Q26">
-        <v>2.2659700608</v>
+        <v>2.25728548</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.116794563546528</v>
+        <v>0.1175579459502542</v>
       </c>
       <c r="T26">
-        <v>1.197070333718567</v>
+        <v>1.209942057737047</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.72014897944182</v>
+        <v>10.29134302026414</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09801045946269062</v>
+        <v>0.09780873063001991</v>
       </c>
       <c r="C27">
-        <v>17.3677372916671</v>
+        <v>17.18491725731702</v>
       </c>
       <c r="D27">
-        <v>18.48273729166711</v>
+        <v>18.52051725731702</v>
       </c>
       <c r="E27">
-        <v>4.055000000000001</v>
+        <v>4.275600000000001</v>
       </c>
       <c r="F27">
-        <v>5.515000000000001</v>
+        <v>5.735600000000001</v>
       </c>
       <c r="G27">
         <v>4.4</v>
@@ -3614,28 +3614,28 @@
         <v>2.94</v>
       </c>
       <c r="M27">
-        <v>0.285677</v>
+        <v>0.29710408</v>
       </c>
       <c r="N27">
-        <v>2.654323</v>
+        <v>2.64289592</v>
       </c>
       <c r="O27">
-        <v>0.6370375199999999</v>
+        <v>0.6342950208</v>
       </c>
       <c r="P27">
-        <v>2.01728548</v>
+        <v>2.0086008992</v>
       </c>
       <c r="Q27">
-        <v>2.25728548</v>
+        <v>2.2486008992</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1175579459502542</v>
+        <v>0.1183419603108377</v>
       </c>
       <c r="T27">
-        <v>1.209942057737047</v>
+        <v>1.223161666188458</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.29134302026414</v>
+        <v>9.895522134869369</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09780873063001991</v>
+        <v>0.09795584179734923</v>
       </c>
       <c r="C28">
-        <v>17.18491725731702</v>
+        <v>16.93675091459782</v>
       </c>
       <c r="D28">
-        <v>18.52051725731702</v>
+        <v>18.49295091459782</v>
       </c>
       <c r="E28">
-        <v>4.275600000000001</v>
+        <v>4.496200000000001</v>
       </c>
       <c r="F28">
-        <v>5.735600000000001</v>
+        <v>5.956200000000001</v>
       </c>
       <c r="G28">
         <v>4.4</v>
@@ -3696,45 +3696,45 @@
         <v>2.94</v>
       </c>
       <c r="M28">
-        <v>0.29710408</v>
+        <v>0.3186567</v>
       </c>
       <c r="N28">
-        <v>2.64289592</v>
+        <v>2.6213433</v>
       </c>
       <c r="O28">
-        <v>0.6342950208</v>
+        <v>0.629122392</v>
       </c>
       <c r="P28">
-        <v>2.0086008992</v>
+        <v>1.992220908</v>
       </c>
       <c r="Q28">
-        <v>2.2486008992</v>
+        <v>2.232220908</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1183419603108377</v>
+        <v>0.1191474545169167</v>
       </c>
       <c r="T28">
-        <v>1.223161666188458</v>
+        <v>1.236743455693332</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.895522134869369</v>
+        <v>9.226229983552832</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09795584179734923</v>
+        <v>0.09776703296467852</v>
       </c>
       <c r="C29">
-        <v>16.93675091459782</v>
+        <v>16.75154570542944</v>
       </c>
       <c r="D29">
-        <v>18.49295091459782</v>
+        <v>18.52834570542944</v>
       </c>
       <c r="E29">
-        <v>4.496200000000001</v>
+        <v>4.716800000000001</v>
       </c>
       <c r="F29">
-        <v>5.956200000000001</v>
+        <v>6.176800000000001</v>
       </c>
       <c r="G29">
         <v>4.4</v>
@@ -3778,28 +3778,28 @@
         <v>2.94</v>
       </c>
       <c r="M29">
-        <v>0.3186567</v>
+        <v>0.3304588000000001</v>
       </c>
       <c r="N29">
-        <v>2.6213433</v>
+        <v>2.6095412</v>
       </c>
       <c r="O29">
-        <v>0.629122392</v>
+        <v>0.626289888</v>
       </c>
       <c r="P29">
-        <v>1.992220908</v>
+        <v>1.983251312</v>
       </c>
       <c r="Q29">
-        <v>2.232220908</v>
+        <v>2.223251312</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1191474545169167</v>
+        <v>0.1199753235620535</v>
       </c>
       <c r="T29">
-        <v>1.236743455693332</v>
+        <v>1.250702517128897</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.226229983552832</v>
+        <v>8.896721769854516</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09776703296467852</v>
+        <v>0.09757822413200783</v>
       </c>
       <c r="C30">
-        <v>16.75154570542944</v>
+        <v>16.56647624459195</v>
       </c>
       <c r="D30">
-        <v>18.52834570542944</v>
+        <v>18.56387624459195</v>
       </c>
       <c r="E30">
-        <v>4.716800000000001</v>
+        <v>4.937400000000001</v>
       </c>
       <c r="F30">
-        <v>6.176800000000001</v>
+        <v>6.397400000000001</v>
       </c>
       <c r="G30">
         <v>4.4</v>
@@ -3860,28 +3860,28 @@
         <v>2.94</v>
       </c>
       <c r="M30">
-        <v>0.3304588000000001</v>
+        <v>0.3422609</v>
       </c>
       <c r="N30">
-        <v>2.6095412</v>
+        <v>2.5977391</v>
       </c>
       <c r="O30">
-        <v>0.626289888</v>
+        <v>0.6234573839999999</v>
       </c>
       <c r="P30">
-        <v>1.983251312</v>
+        <v>1.974281716</v>
       </c>
       <c r="Q30">
-        <v>2.223251312</v>
+        <v>2.214281716</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1199753235620535</v>
+        <v>0.1208265128619828</v>
       </c>
       <c r="T30">
-        <v>1.250702517128897</v>
+        <v>1.265054791562648</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.896721769854516</v>
+        <v>8.589938260549189</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09757822413200781</v>
+        <v>0.09738941529933712</v>
       </c>
       <c r="C31">
-        <v>16.56647624459195</v>
+        <v>16.3815433145316</v>
       </c>
       <c r="D31">
-        <v>18.56387624459195</v>
+        <v>18.59954331453161</v>
       </c>
       <c r="E31">
-        <v>4.9374</v>
+        <v>5.158</v>
       </c>
       <c r="F31">
-        <v>6.3974</v>
+        <v>6.618</v>
       </c>
       <c r="G31">
         <v>4.4</v>
@@ -3942,28 +3942,28 @@
         <v>2.94</v>
       </c>
       <c r="M31">
-        <v>0.3422609</v>
+        <v>0.354063</v>
       </c>
       <c r="N31">
-        <v>2.5977391</v>
+        <v>2.585937</v>
       </c>
       <c r="O31">
-        <v>0.6234573839999999</v>
+        <v>0.6206248799999999</v>
       </c>
       <c r="P31">
-        <v>1.974281716</v>
+        <v>1.96531212</v>
       </c>
       <c r="Q31">
-        <v>2.214281716</v>
+        <v>2.20531212</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1208265128619828</v>
+        <v>0.1217020218561959</v>
       </c>
       <c r="T31">
-        <v>1.265054791562648</v>
+        <v>1.279817130980219</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.589938260549189</v>
+        <v>8.303606985197549</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09738941529933712</v>
+        <v>0.09720060646666642</v>
       </c>
       <c r="C32">
-        <v>16.3815433145316</v>
+        <v>16.19674770371956</v>
       </c>
       <c r="D32">
-        <v>18.59954331453161</v>
+        <v>18.63534770371956</v>
       </c>
       <c r="E32">
-        <v>5.158</v>
+        <v>5.3786</v>
       </c>
       <c r="F32">
-        <v>6.618</v>
+        <v>6.8386</v>
       </c>
       <c r="G32">
         <v>4.4</v>
@@ -4024,28 +4024,28 @@
         <v>2.94</v>
       </c>
       <c r="M32">
-        <v>0.354063</v>
+        <v>0.3658651</v>
       </c>
       <c r="N32">
-        <v>2.585937</v>
+        <v>2.5741349</v>
       </c>
       <c r="O32">
-        <v>0.6206248799999999</v>
+        <v>0.6177923759999999</v>
       </c>
       <c r="P32">
-        <v>1.96531212</v>
+        <v>1.956342524</v>
       </c>
       <c r="Q32">
-        <v>2.20531212</v>
+        <v>2.196342524</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1217020218561959</v>
+        <v>0.122602907922705</v>
       </c>
       <c r="T32">
-        <v>1.279817130980219</v>
+        <v>1.295007364293953</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.303606985197549</v>
+        <v>8.035748695352467</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09720060646666642</v>
+        <v>0.09701179763399573</v>
       </c>
       <c r="C33">
-        <v>16.19674770371956</v>
+        <v>16.01209020670994</v>
       </c>
       <c r="D33">
-        <v>18.63534770371956</v>
+        <v>18.67129020670994</v>
       </c>
       <c r="E33">
-        <v>5.3786</v>
+        <v>5.599200000000001</v>
       </c>
       <c r="F33">
-        <v>6.8386</v>
+        <v>7.059200000000001</v>
       </c>
       <c r="G33">
         <v>4.4</v>
@@ -4106,28 +4106,28 @@
         <v>2.94</v>
       </c>
       <c r="M33">
-        <v>0.3658651</v>
+        <v>0.3776672</v>
       </c>
       <c r="N33">
-        <v>2.5741349</v>
+        <v>2.5623328</v>
       </c>
       <c r="O33">
-        <v>0.6177923759999999</v>
+        <v>0.614959872</v>
       </c>
       <c r="P33">
-        <v>1.956342524</v>
+        <v>1.947372928</v>
       </c>
       <c r="Q33">
-        <v>2.196342524</v>
+        <v>2.187372928</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.122602907922705</v>
+        <v>0.123530290638229</v>
       </c>
       <c r="T33">
-        <v>1.295007364293953</v>
+        <v>1.310644369175737</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.035748695352467</v>
+        <v>7.784631548622702</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09701179763399573</v>
+        <v>0.09702362880132501</v>
       </c>
       <c r="C34">
-        <v>16.01209020670994</v>
+        <v>15.78923390095551</v>
       </c>
       <c r="D34">
-        <v>18.67129020670994</v>
+        <v>18.66903390095551</v>
       </c>
       <c r="E34">
-        <v>5.599200000000001</v>
+        <v>5.819800000000001</v>
       </c>
       <c r="F34">
-        <v>7.059200000000001</v>
+        <v>7.279800000000001</v>
       </c>
       <c r="G34">
         <v>4.4</v>
@@ -4188,45 +4188,45 @@
         <v>2.94</v>
       </c>
       <c r="M34">
-        <v>0.3776672</v>
+        <v>0.39529314</v>
       </c>
       <c r="N34">
-        <v>2.5623328</v>
+        <v>2.54470686</v>
       </c>
       <c r="O34">
-        <v>0.614959872</v>
+        <v>0.6107296463999999</v>
       </c>
       <c r="P34">
-        <v>1.947372928</v>
+        <v>1.9339772136</v>
       </c>
       <c r="Q34">
-        <v>2.187372928</v>
+        <v>2.1739772136</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.123530290638229</v>
+        <v>0.1244853564198881</v>
       </c>
       <c r="T34">
-        <v>1.310644369175737</v>
+        <v>1.326748150322649</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.784631548622702</v>
+        <v>7.437518394576743</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09702362880132501</v>
+        <v>0.0968408999686543</v>
       </c>
       <c r="C35">
-        <v>15.78923390095551</v>
+        <v>15.60354280953115</v>
       </c>
       <c r="D35">
-        <v>18.66903390095551</v>
+        <v>18.70394280953116</v>
       </c>
       <c r="E35">
-        <v>5.819800000000001</v>
+        <v>6.040400000000002</v>
       </c>
       <c r="F35">
-        <v>7.279800000000001</v>
+        <v>7.500400000000002</v>
       </c>
       <c r="G35">
         <v>4.4</v>
@@ -4270,28 +4270,28 @@
         <v>2.94</v>
       </c>
       <c r="M35">
-        <v>0.39529314</v>
+        <v>0.4072717200000001</v>
       </c>
       <c r="N35">
-        <v>2.54470686</v>
+        <v>2.53272828</v>
       </c>
       <c r="O35">
-        <v>0.6107296463999999</v>
+        <v>0.6078547871999999</v>
       </c>
       <c r="P35">
-        <v>1.9339772136</v>
+        <v>1.9248734928</v>
       </c>
       <c r="Q35">
-        <v>2.1739772136</v>
+        <v>2.1648734928</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1244853564198881</v>
+        <v>0.1254693635888702</v>
       </c>
       <c r="T35">
-        <v>1.326748150322649</v>
+        <v>1.343339924837649</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.437518394576743</v>
+        <v>7.218767853559778</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0968408999686543</v>
+        <v>0.09665817113598361</v>
       </c>
       <c r="C36">
-        <v>15.60354280953115</v>
+        <v>15.41798251382685</v>
       </c>
       <c r="D36">
-        <v>18.70394280953116</v>
+        <v>18.73898251382685</v>
       </c>
       <c r="E36">
-        <v>6.040400000000002</v>
+        <v>6.261000000000002</v>
       </c>
       <c r="F36">
-        <v>7.500400000000002</v>
+        <v>7.721000000000002</v>
       </c>
       <c r="G36">
         <v>4.4</v>
@@ -4352,28 +4352,28 @@
         <v>2.94</v>
       </c>
       <c r="M36">
-        <v>0.4072717200000001</v>
+        <v>0.4192503000000001</v>
       </c>
       <c r="N36">
-        <v>2.53272828</v>
+        <v>2.5207497</v>
       </c>
       <c r="O36">
-        <v>0.6078547871999999</v>
+        <v>0.6049799279999999</v>
       </c>
       <c r="P36">
-        <v>1.9248734928</v>
+        <v>1.915769772</v>
       </c>
       <c r="Q36">
-        <v>2.1648734928</v>
+        <v>2.155769772</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1254693635888702</v>
+        <v>0.1264836479015133</v>
       </c>
       <c r="T36">
-        <v>1.343339924837649</v>
+        <v>1.360442215491573</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.218767853559778</v>
+        <v>7.01251734345807</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09665817113598361</v>
+        <v>0.09647544230331291</v>
       </c>
       <c r="C37">
-        <v>15.41798251382685</v>
+        <v>15.2325537503149</v>
       </c>
       <c r="D37">
-        <v>18.73898251382685</v>
+        <v>18.7741537503149</v>
       </c>
       <c r="E37">
-        <v>6.261000000000002</v>
+        <v>6.481600000000002</v>
       </c>
       <c r="F37">
-        <v>7.721000000000002</v>
+        <v>7.941600000000002</v>
       </c>
       <c r="G37">
         <v>4.4</v>
@@ -4434,28 +4434,28 @@
         <v>2.94</v>
       </c>
       <c r="M37">
-        <v>0.4192503000000001</v>
+        <v>0.4312288800000001</v>
       </c>
       <c r="N37">
-        <v>2.5207497</v>
+        <v>2.50877112</v>
       </c>
       <c r="O37">
-        <v>0.6049799279999999</v>
+        <v>0.6021050688</v>
       </c>
       <c r="P37">
-        <v>1.915769772</v>
+        <v>1.9066660512</v>
       </c>
       <c r="Q37">
-        <v>2.155769772</v>
+        <v>2.1466660512</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1264836479015133</v>
+        <v>0.1275296285989264</v>
       </c>
       <c r="T37">
-        <v>1.360442215491573</v>
+        <v>1.378078952728432</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.01251734345807</v>
+        <v>6.817725195028681</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09647544230331292</v>
+        <v>0.09629271347064222</v>
       </c>
       <c r="C38">
-        <v>15.2325537503149</v>
+        <v>15.04725726100714</v>
       </c>
       <c r="D38">
-        <v>18.7741537503149</v>
+        <v>18.80945726100715</v>
       </c>
       <c r="E38">
-        <v>6.4816</v>
+        <v>6.7022</v>
       </c>
       <c r="F38">
-        <v>7.9416</v>
+        <v>8.1622</v>
       </c>
       <c r="G38">
         <v>4.4</v>
@@ -4516,28 +4516,28 @@
         <v>2.94</v>
       </c>
       <c r="M38">
-        <v>0.43122888</v>
+        <v>0.4432074600000001</v>
       </c>
       <c r="N38">
-        <v>2.50877112</v>
+        <v>2.49679254</v>
       </c>
       <c r="O38">
-        <v>0.6021050688</v>
+        <v>0.5992302096</v>
       </c>
       <c r="P38">
-        <v>1.9066660512</v>
+        <v>1.8975623304</v>
       </c>
       <c r="Q38">
-        <v>2.1466660512</v>
+        <v>2.1375623304</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1275296285989264</v>
+        <v>0.1286088150327654</v>
       </c>
       <c r="T38">
-        <v>1.378078952728431</v>
+        <v>1.396275586385508</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.817725195028681</v>
+        <v>6.633462351919798</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09629271347064222</v>
+        <v>0.09610998463797152</v>
       </c>
       <c r="C39">
-        <v>15.04725726100714</v>
+        <v>14.86209379350717</v>
       </c>
       <c r="D39">
-        <v>18.80945726100715</v>
+        <v>18.84489379350717</v>
       </c>
       <c r="E39">
-        <v>6.7022</v>
+        <v>6.922800000000001</v>
       </c>
       <c r="F39">
-        <v>8.1622</v>
+        <v>8.382800000000001</v>
       </c>
       <c r="G39">
         <v>4.4</v>
@@ -4598,28 +4598,28 @@
         <v>2.94</v>
       </c>
       <c r="M39">
-        <v>0.4432074600000001</v>
+        <v>0.4551860400000001</v>
       </c>
       <c r="N39">
-        <v>2.49679254</v>
+        <v>2.48481396</v>
       </c>
       <c r="O39">
-        <v>0.5992302096</v>
+        <v>0.5963553504</v>
       </c>
       <c r="P39">
-        <v>1.8975623304</v>
+        <v>1.8884586096</v>
       </c>
       <c r="Q39">
-        <v>2.1375623304</v>
+        <v>2.1284586096</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1286088150327654</v>
+        <v>0.1297228139322121</v>
       </c>
       <c r="T39">
-        <v>1.396275586385508</v>
+        <v>1.41505920822507</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.633462351919798</v>
+        <v>6.458897553185066</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09610998463797152</v>
+        <v>0.09592725580530083</v>
       </c>
       <c r="C40">
-        <v>14.86209379350717</v>
+        <v>14.67706410106302</v>
       </c>
       <c r="D40">
-        <v>18.84489379350717</v>
+        <v>18.88046410106302</v>
       </c>
       <c r="E40">
-        <v>6.922800000000001</v>
+        <v>7.143400000000001</v>
       </c>
       <c r="F40">
-        <v>8.382800000000001</v>
+        <v>8.603400000000001</v>
       </c>
       <c r="G40">
         <v>4.4</v>
@@ -4680,28 +4680,28 @@
         <v>2.94</v>
       </c>
       <c r="M40">
-        <v>0.4551860400000001</v>
+        <v>0.46716462</v>
       </c>
       <c r="N40">
-        <v>2.48481396</v>
+        <v>2.47283538</v>
       </c>
       <c r="O40">
-        <v>0.5963553504</v>
+        <v>0.5934804911999999</v>
       </c>
       <c r="P40">
-        <v>1.8884586096</v>
+        <v>1.8793548888</v>
       </c>
       <c r="Q40">
-        <v>2.1284586096</v>
+        <v>2.1193548888</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1297228139322121</v>
+        <v>0.1308733373857391</v>
       </c>
       <c r="T40">
-        <v>1.41505920822507</v>
+        <v>1.434458686518389</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.458897553185066</v>
+        <v>6.29328479541109</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09592725580530083</v>
+        <v>0.09574452697263011</v>
       </c>
       <c r="C41">
-        <v>14.67706410106302</v>
+        <v>14.49216894262065</v>
       </c>
       <c r="D41">
-        <v>18.88046410106302</v>
+        <v>18.91616894262066</v>
       </c>
       <c r="E41">
-        <v>7.143400000000001</v>
+        <v>7.364000000000002</v>
       </c>
       <c r="F41">
-        <v>8.603400000000001</v>
+        <v>8.824000000000002</v>
       </c>
       <c r="G41">
         <v>4.4</v>
@@ -4762,28 +4762,28 @@
         <v>2.94</v>
       </c>
       <c r="M41">
-        <v>0.46716462</v>
+        <v>0.4791432000000001</v>
       </c>
       <c r="N41">
-        <v>2.47283538</v>
+        <v>2.4608568</v>
       </c>
       <c r="O41">
-        <v>0.5934804911999999</v>
+        <v>0.5906056319999999</v>
       </c>
       <c r="P41">
-        <v>1.8793548888</v>
+        <v>1.870251168</v>
       </c>
       <c r="Q41">
-        <v>2.1193548888</v>
+        <v>2.110251168</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1308733373857391</v>
+        <v>0.1320622116210502</v>
       </c>
       <c r="T41">
-        <v>1.434458686518389</v>
+        <v>1.454504814088152</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.29328479541109</v>
+        <v>6.135952675525812</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09574452697263011</v>
+        <v>0.09587339813995942</v>
       </c>
       <c r="C42">
-        <v>14.49216894262065</v>
+        <v>14.24637376222936</v>
       </c>
       <c r="D42">
-        <v>18.91616894262066</v>
+        <v>18.89097376222936</v>
       </c>
       <c r="E42">
-        <v>7.364000000000002</v>
+        <v>7.584600000000001</v>
       </c>
       <c r="F42">
-        <v>8.824000000000002</v>
+        <v>9.044600000000001</v>
       </c>
       <c r="G42">
         <v>4.4</v>
@@ -4844,45 +4844,45 @@
         <v>2.94</v>
       </c>
       <c r="M42">
-        <v>0.4791432000000001</v>
+        <v>0.50016638</v>
       </c>
       <c r="N42">
-        <v>2.4608568</v>
+        <v>2.43983362</v>
       </c>
       <c r="O42">
-        <v>0.5906056319999999</v>
+        <v>0.5855600688</v>
       </c>
       <c r="P42">
-        <v>1.870251168</v>
+        <v>1.8542735512</v>
       </c>
       <c r="Q42">
-        <v>2.110251168</v>
+        <v>2.0942735512</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1320622116210502</v>
+        <v>0.1332913866778973</v>
       </c>
       <c r="T42">
-        <v>1.454504814088152</v>
+        <v>1.475230471406042</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.135952675525812</v>
+        <v>5.878044022071215</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09587339813995942</v>
+        <v>0.09569826930728872</v>
       </c>
       <c r="C43">
-        <v>14.24637376222936</v>
+        <v>14.06002902650322</v>
       </c>
       <c r="D43">
-        <v>18.89097376222936</v>
+        <v>18.92522902650322</v>
       </c>
       <c r="E43">
-        <v>7.584600000000001</v>
+        <v>7.805200000000002</v>
       </c>
       <c r="F43">
-        <v>9.044600000000001</v>
+        <v>9.265200000000002</v>
       </c>
       <c r="G43">
         <v>4.4</v>
@@ -4926,28 +4926,28 @@
         <v>2.94</v>
       </c>
       <c r="M43">
-        <v>0.50016638</v>
+        <v>0.5123655600000001</v>
       </c>
       <c r="N43">
-        <v>2.43983362</v>
+        <v>2.42763444</v>
       </c>
       <c r="O43">
-        <v>0.5855600688</v>
+        <v>0.5826322655999999</v>
       </c>
       <c r="P43">
-        <v>1.8542735512</v>
+        <v>1.8450021744</v>
       </c>
       <c r="Q43">
-        <v>2.0942735512</v>
+        <v>2.0850021744</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1332913866778973</v>
+        <v>0.1345629470815323</v>
       </c>
       <c r="T43">
-        <v>1.475230471406042</v>
+        <v>1.49667080656248</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.878044022071215</v>
+        <v>5.738090592974281</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09569826930728872</v>
+        <v>0.09552314047461803</v>
       </c>
       <c r="C44">
-        <v>14.06002902650322</v>
+        <v>13.87380874754623</v>
       </c>
       <c r="D44">
-        <v>18.92522902650322</v>
+        <v>18.95960874754623</v>
       </c>
       <c r="E44">
-        <v>7.8052</v>
+        <v>8.0258</v>
       </c>
       <c r="F44">
-        <v>9.2652</v>
+        <v>9.485800000000001</v>
       </c>
       <c r="G44">
         <v>4.4</v>
@@ -5008,28 +5008,28 @@
         <v>2.94</v>
       </c>
       <c r="M44">
-        <v>0.51236556</v>
+        <v>0.5245647400000001</v>
       </c>
       <c r="N44">
-        <v>2.42763444</v>
+        <v>2.41543526</v>
       </c>
       <c r="O44">
-        <v>0.5826322655999999</v>
+        <v>0.5797044624</v>
       </c>
       <c r="P44">
-        <v>1.8450021744</v>
+        <v>1.8357307976</v>
       </c>
       <c r="Q44">
-        <v>2.0850021744</v>
+        <v>2.0757307976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1345629470815323</v>
+        <v>0.1358791236396807</v>
       </c>
       <c r="T44">
-        <v>1.49667080656248</v>
+        <v>1.518863434180548</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.738090592974282</v>
+        <v>5.604646625695809</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09552314047461803</v>
+        <v>0.09534801164194733</v>
       </c>
       <c r="C45">
-        <v>13.87380874754623</v>
+        <v>13.68771360486023</v>
       </c>
       <c r="D45">
-        <v>18.95960874754623</v>
+        <v>18.99411360486023</v>
       </c>
       <c r="E45">
-        <v>8.0258</v>
+        <v>8.246400000000001</v>
       </c>
       <c r="F45">
-        <v>9.485800000000001</v>
+        <v>9.7064</v>
       </c>
       <c r="G45">
         <v>4.4</v>
@@ -5090,28 +5090,28 @@
         <v>2.94</v>
       </c>
       <c r="M45">
-        <v>0.5245647400000001</v>
+        <v>0.5367639200000001</v>
       </c>
       <c r="N45">
-        <v>2.41543526</v>
+        <v>2.40323608</v>
       </c>
       <c r="O45">
-        <v>0.5797044624</v>
+        <v>0.5767766592</v>
       </c>
       <c r="P45">
-        <v>1.8357307976</v>
+        <v>1.8264594208</v>
       </c>
       <c r="Q45">
-        <v>2.0757307976</v>
+        <v>2.0664594208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1358791236396807</v>
+        <v>0.1372423065034774</v>
       </c>
       <c r="T45">
-        <v>1.518863434180548</v>
+        <v>1.541848655642118</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.604646625695809</v>
+        <v>5.477268293293633</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09534801164194733</v>
+        <v>0.09517288280927665</v>
       </c>
       <c r="C46">
-        <v>13.68771360486023</v>
+        <v>13.50174428290263</v>
       </c>
       <c r="D46">
-        <v>18.99411360486023</v>
+        <v>19.02874428290263</v>
       </c>
       <c r="E46">
-        <v>8.246400000000001</v>
+        <v>8.467000000000002</v>
       </c>
       <c r="F46">
-        <v>9.7064</v>
+        <v>9.927000000000001</v>
       </c>
       <c r="G46">
         <v>4.4</v>
@@ -5172,28 +5172,28 @@
         <v>2.94</v>
       </c>
       <c r="M46">
-        <v>0.5367639200000001</v>
+        <v>0.5489631000000001</v>
       </c>
       <c r="N46">
-        <v>2.40323608</v>
+        <v>2.3910369</v>
       </c>
       <c r="O46">
-        <v>0.5767766592</v>
+        <v>0.5738488559999999</v>
       </c>
       <c r="P46">
-        <v>1.8264594208</v>
+        <v>1.817188044</v>
       </c>
       <c r="Q46">
-        <v>2.0664594208</v>
+        <v>2.057188044</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1372423065034774</v>
+        <v>0.1386550596532302</v>
       </c>
       <c r="T46">
-        <v>1.541848655642118</v>
+        <v>1.565669703338654</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.477268293293633</v>
+        <v>5.355551220109327</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09517288280927665</v>
+        <v>0.09499775397660593</v>
       </c>
       <c r="C47">
-        <v>13.50174428290263</v>
+        <v>13.31590147113166</v>
       </c>
       <c r="D47">
-        <v>19.02874428290263</v>
+        <v>19.06350147113166</v>
       </c>
       <c r="E47">
-        <v>8.467000000000002</v>
+        <v>8.6876</v>
       </c>
       <c r="F47">
-        <v>9.927000000000001</v>
+        <v>10.1476</v>
       </c>
       <c r="G47">
         <v>4.4</v>
@@ -5254,28 +5254,28 @@
         <v>2.94</v>
       </c>
       <c r="M47">
-        <v>0.5489631000000001</v>
+        <v>0.56116228</v>
       </c>
       <c r="N47">
-        <v>2.3910369</v>
+        <v>2.37883772</v>
       </c>
       <c r="O47">
-        <v>0.5738488559999999</v>
+        <v>0.5709210527999999</v>
       </c>
       <c r="P47">
-        <v>1.817188044</v>
+        <v>1.8079166672</v>
       </c>
       <c r="Q47">
-        <v>2.057188044</v>
+        <v>2.0479166672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1386550596532302</v>
+        <v>0.1401201369937147</v>
       </c>
       <c r="T47">
-        <v>1.565669703338654</v>
+        <v>1.590373012060988</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.355551220109327</v>
+        <v>5.239126193585213</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09499775397660593</v>
+        <v>0.09482262514393523</v>
       </c>
       <c r="C48">
-        <v>13.31590147113166</v>
+        <v>13.13018586405209</v>
       </c>
       <c r="D48">
-        <v>19.06350147113166</v>
+        <v>19.0983858640521</v>
       </c>
       <c r="E48">
-        <v>8.6876</v>
+        <v>8.908200000000001</v>
       </c>
       <c r="F48">
-        <v>10.1476</v>
+        <v>10.3682</v>
       </c>
       <c r="G48">
         <v>4.4</v>
@@ -5336,28 +5336,28 @@
         <v>2.94</v>
       </c>
       <c r="M48">
-        <v>0.56116228</v>
+        <v>0.5733614600000001</v>
       </c>
       <c r="N48">
-        <v>2.37883772</v>
+        <v>2.36663854</v>
       </c>
       <c r="O48">
-        <v>0.5709210527999999</v>
+        <v>0.5679932496</v>
       </c>
       <c r="P48">
-        <v>1.8079166672</v>
+        <v>1.7986452904</v>
       </c>
       <c r="Q48">
-        <v>2.0479166672</v>
+        <v>2.0386452904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1401201369937147</v>
+        <v>0.1416405002715759</v>
       </c>
       <c r="T48">
-        <v>1.590373012060988</v>
+        <v>1.616008521112466</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.239126193585213</v>
+        <v>5.127655423508932</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09482262514393523</v>
+        <v>0.09464749631126453</v>
       </c>
       <c r="C49">
-        <v>13.13018586405209</v>
+        <v>12.94459816126158</v>
       </c>
       <c r="D49">
-        <v>19.0983858640521</v>
+        <v>19.13339816126159</v>
       </c>
       <c r="E49">
-        <v>8.908200000000001</v>
+        <v>9.128800000000002</v>
       </c>
       <c r="F49">
-        <v>10.3682</v>
+        <v>10.5888</v>
       </c>
       <c r="G49">
         <v>4.4</v>
@@ -5418,28 +5418,28 @@
         <v>2.94</v>
       </c>
       <c r="M49">
-        <v>0.5733614600000001</v>
+        <v>0.5855606400000002</v>
       </c>
       <c r="N49">
-        <v>2.36663854</v>
+        <v>2.35443936</v>
       </c>
       <c r="O49">
-        <v>0.5679932496</v>
+        <v>0.5650654463999999</v>
       </c>
       <c r="P49">
-        <v>1.7986452904</v>
+        <v>1.7893739136</v>
       </c>
       <c r="Q49">
-        <v>2.0386452904</v>
+        <v>2.0293739136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1416405002715759</v>
+        <v>0.1432193390601241</v>
       </c>
       <c r="T49">
-        <v>1.616008521112466</v>
+        <v>1.642630011281309</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.127655423508932</v>
+        <v>5.020829268852495</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09464749631126453</v>
+        <v>0.09447236747859382</v>
       </c>
       <c r="C50">
-        <v>12.94459816126159</v>
+        <v>12.75913906749734</v>
       </c>
       <c r="D50">
-        <v>19.13339816126159</v>
+        <v>19.16853906749734</v>
       </c>
       <c r="E50">
-        <v>9.128800000000002</v>
+        <v>9.349399999999999</v>
       </c>
       <c r="F50">
-        <v>10.5888</v>
+        <v>10.8094</v>
       </c>
       <c r="G50">
         <v>4.4</v>
@@ -5500,28 +5500,28 @@
         <v>2.94</v>
       </c>
       <c r="M50">
-        <v>0.5855606400000001</v>
+        <v>0.5977598200000001</v>
       </c>
       <c r="N50">
-        <v>2.35443936</v>
+        <v>2.34224018</v>
       </c>
       <c r="O50">
-        <v>0.5650654463999999</v>
+        <v>0.5621376432</v>
       </c>
       <c r="P50">
-        <v>1.7893739136</v>
+        <v>1.7801025368</v>
       </c>
       <c r="Q50">
-        <v>2.0293739136</v>
+        <v>2.020102536800001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1432193390601241</v>
+        <v>0.144860093095282</v>
       </c>
       <c r="T50">
-        <v>1.642630011281309</v>
+        <v>1.670295481456774</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.020829268852496</v>
+        <v>4.918363365406528</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09447236747859382</v>
+        <v>0.09429723864592313</v>
       </c>
       <c r="C51">
-        <v>12.75913906749734</v>
+        <v>12.57380929268346</v>
       </c>
       <c r="D51">
-        <v>19.16853906749734</v>
+        <v>19.20380929268346</v>
       </c>
       <c r="E51">
-        <v>9.349399999999999</v>
+        <v>9.57</v>
       </c>
       <c r="F51">
-        <v>10.8094</v>
+        <v>11.03</v>
       </c>
       <c r="G51">
         <v>4.4</v>
@@ -5582,28 +5582,28 @@
         <v>2.94</v>
       </c>
       <c r="M51">
-        <v>0.5977598200000001</v>
+        <v>0.609959</v>
       </c>
       <c r="N51">
-        <v>2.34224018</v>
+        <v>2.330041</v>
       </c>
       <c r="O51">
-        <v>0.5621376432</v>
+        <v>0.55920984</v>
       </c>
       <c r="P51">
-        <v>1.7801025368</v>
+        <v>1.77083116</v>
       </c>
       <c r="Q51">
-        <v>2.020102536800001</v>
+        <v>2.01083116</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.144860093095282</v>
+        <v>0.1465664772918462</v>
       </c>
       <c r="T51">
-        <v>1.670295481456774</v>
+        <v>1.699067570439257</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.918363365406528</v>
+        <v>4.819996098098397</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09429723864592313</v>
+        <v>0.09412210981325243</v>
       </c>
       <c r="C52">
-        <v>12.57380929268346</v>
+        <v>12.38860955197874</v>
       </c>
       <c r="D52">
-        <v>19.20380929268346</v>
+        <v>19.23920955197875</v>
       </c>
       <c r="E52">
-        <v>9.57</v>
+        <v>9.790600000000001</v>
       </c>
       <c r="F52">
-        <v>11.03</v>
+        <v>11.2506</v>
       </c>
       <c r="G52">
         <v>4.4</v>
@@ -5664,28 +5664,28 @@
         <v>2.94</v>
       </c>
       <c r="M52">
-        <v>0.609959</v>
+        <v>0.6221581800000001</v>
       </c>
       <c r="N52">
-        <v>2.330041</v>
+        <v>2.31784182</v>
       </c>
       <c r="O52">
-        <v>0.55920984</v>
+        <v>0.5562820368</v>
       </c>
       <c r="P52">
-        <v>1.77083116</v>
+        <v>1.7615597832</v>
       </c>
       <c r="Q52">
-        <v>2.01083116</v>
+        <v>2.0015597832</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1465664772918462</v>
+        <v>0.1483425098229642</v>
       </c>
       <c r="T52">
-        <v>1.699067570439257</v>
+        <v>1.729014030400617</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.819996098098397</v>
+        <v>4.725486370684703</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09412210981325243</v>
+        <v>0.09394698098058174</v>
       </c>
       <c r="C53">
-        <v>12.38860955197874</v>
+        <v>12.20354056582502</v>
       </c>
       <c r="D53">
-        <v>19.23920955197875</v>
+        <v>19.27474056582502</v>
       </c>
       <c r="E53">
-        <v>9.790600000000001</v>
+        <v>10.0112</v>
       </c>
       <c r="F53">
-        <v>11.2506</v>
+        <v>11.4712</v>
       </c>
       <c r="G53">
         <v>4.4</v>
@@ -5746,28 +5746,28 @@
         <v>2.94</v>
       </c>
       <c r="M53">
-        <v>0.6221581800000001</v>
+        <v>0.6343573600000001</v>
       </c>
       <c r="N53">
-        <v>2.31784182</v>
+        <v>2.30564264</v>
       </c>
       <c r="O53">
-        <v>0.5562820368</v>
+        <v>0.5533542335999999</v>
       </c>
       <c r="P53">
-        <v>1.7615597832</v>
+        <v>1.7522884064</v>
       </c>
       <c r="Q53">
-        <v>2.0015597832</v>
+        <v>1.9922884064</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1483425098229642</v>
+        <v>0.1501925437095453</v>
       </c>
       <c r="T53">
-        <v>1.729014030400617</v>
+        <v>1.760208259527033</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.725486370684703</v>
+        <v>4.634611632786919</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09394698098058174</v>
+        <v>0.09377185214791103</v>
       </c>
       <c r="C54">
-        <v>12.20354056582502</v>
+        <v>12.01860305999602</v>
       </c>
       <c r="D54">
-        <v>19.27474056582502</v>
+        <v>19.31040305999602</v>
       </c>
       <c r="E54">
-        <v>10.0112</v>
+        <v>10.2318</v>
       </c>
       <c r="F54">
-        <v>11.4712</v>
+        <v>11.6918</v>
       </c>
       <c r="G54">
         <v>4.4</v>
@@ -5828,28 +5828,28 @@
         <v>2.94</v>
       </c>
       <c r="M54">
-        <v>0.6343573600000001</v>
+        <v>0.6465565400000002</v>
       </c>
       <c r="N54">
-        <v>2.30564264</v>
+        <v>2.29344346</v>
       </c>
       <c r="O54">
-        <v>0.5533542335999999</v>
+        <v>0.5504264303999999</v>
       </c>
       <c r="P54">
-        <v>1.7522884064</v>
+        <v>1.7430170296</v>
       </c>
       <c r="Q54">
-        <v>1.9922884064</v>
+        <v>1.9830170296</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1501925437095453</v>
+        <v>0.1521213024423639</v>
       </c>
       <c r="T54">
-        <v>1.760208259527033</v>
+        <v>1.792729902658829</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.634611632786919</v>
+        <v>4.547166130281505</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09377185214791103</v>
+        <v>0.09462272331524033</v>
       </c>
       <c r="C55">
-        <v>12.01860305999602</v>
+        <v>11.62596122177186</v>
       </c>
       <c r="D55">
-        <v>19.31040305999602</v>
+        <v>19.13836122177186</v>
       </c>
       <c r="E55">
-        <v>10.2318</v>
+        <v>10.4524</v>
       </c>
       <c r="F55">
-        <v>11.6918</v>
+        <v>11.9124</v>
       </c>
       <c r="G55">
         <v>4.4</v>
@@ -5910,45 +5910,45 @@
         <v>2.94</v>
       </c>
       <c r="M55">
-        <v>0.6465565400000002</v>
+        <v>0.6885367200000001</v>
       </c>
       <c r="N55">
-        <v>2.29344346</v>
+        <v>2.25146328</v>
       </c>
       <c r="O55">
-        <v>0.5504264303999999</v>
+        <v>0.5403511872</v>
       </c>
       <c r="P55">
-        <v>1.7430170296</v>
+        <v>1.7111120928</v>
       </c>
       <c r="Q55">
-        <v>1.9830170296</v>
+        <v>1.9511120928</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1521213024423639</v>
+        <v>0.1541339202505225</v>
       </c>
       <c r="T55">
-        <v>1.792729902658829</v>
+        <v>1.826665530274616</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.547166130281505</v>
+        <v>4.269924776125229</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09462272331524033</v>
+        <v>0.09446659448256962</v>
       </c>
       <c r="C56">
-        <v>11.62596122177186</v>
+        <v>11.43669966000389</v>
       </c>
       <c r="D56">
-        <v>19.13836122177186</v>
+        <v>19.16969966000389</v>
       </c>
       <c r="E56">
-        <v>10.4524</v>
+        <v>10.673</v>
       </c>
       <c r="F56">
-        <v>11.9124</v>
+        <v>12.133</v>
       </c>
       <c r="G56">
         <v>4.4</v>
@@ -5992,28 +5992,28 @@
         <v>2.94</v>
       </c>
       <c r="M56">
-        <v>0.6885367200000001</v>
+        <v>0.7012874000000002</v>
       </c>
       <c r="N56">
-        <v>2.25146328</v>
+        <v>2.238712599999999</v>
       </c>
       <c r="O56">
-        <v>0.5403511872</v>
+        <v>0.5372910239999998</v>
       </c>
       <c r="P56">
-        <v>1.7111120928</v>
+        <v>1.701421576</v>
       </c>
       <c r="Q56">
-        <v>1.9511120928</v>
+        <v>1.941421576</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1541339202505225</v>
+        <v>0.1562359877390436</v>
       </c>
       <c r="T56">
-        <v>1.826665530274616</v>
+        <v>1.86210940800666</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.269924776125229</v>
+        <v>4.192289780195678</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09446659448256962</v>
+        <v>0.09431046564989892</v>
       </c>
       <c r="C57">
-        <v>11.43669966000389</v>
+        <v>11.24754089789466</v>
       </c>
       <c r="D57">
-        <v>19.16969966000389</v>
+        <v>19.20114089789466</v>
       </c>
       <c r="E57">
-        <v>10.673</v>
+        <v>10.8936</v>
       </c>
       <c r="F57">
-        <v>12.133</v>
+        <v>12.3536</v>
       </c>
       <c r="G57">
         <v>4.4</v>
@@ -6074,28 +6074,28 @@
         <v>2.94</v>
       </c>
       <c r="M57">
-        <v>0.7012874000000002</v>
+        <v>0.7140380800000001</v>
       </c>
       <c r="N57">
-        <v>2.238712599999999</v>
+        <v>2.22596192</v>
       </c>
       <c r="O57">
-        <v>0.5372910239999998</v>
+        <v>0.5342308607999999</v>
       </c>
       <c r="P57">
-        <v>1.701421576</v>
+        <v>1.6917310592</v>
       </c>
       <c r="Q57">
-        <v>1.941421576</v>
+        <v>1.9317310592</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1562359877390436</v>
+        <v>0.1584336037497703</v>
       </c>
       <c r="T57">
-        <v>1.86210940800666</v>
+        <v>1.899164371090161</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.192289780195678</v>
+        <v>4.117427462692184</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09431046564989892</v>
+        <v>0.09415433681722822</v>
       </c>
       <c r="C58">
-        <v>11.24754089789466</v>
+        <v>11.05848544209662</v>
       </c>
       <c r="D58">
-        <v>19.20114089789466</v>
+        <v>19.23268544209662</v>
       </c>
       <c r="E58">
-        <v>10.8936</v>
+        <v>11.1142</v>
       </c>
       <c r="F58">
-        <v>12.3536</v>
+        <v>12.5742</v>
       </c>
       <c r="G58">
         <v>4.4</v>
@@ -6156,28 +6156,28 @@
         <v>2.94</v>
       </c>
       <c r="M58">
-        <v>0.7140380800000001</v>
+        <v>0.7267887600000003</v>
       </c>
       <c r="N58">
-        <v>2.22596192</v>
+        <v>2.21321124</v>
       </c>
       <c r="O58">
-        <v>0.5342308607999999</v>
+        <v>0.5311706975999999</v>
       </c>
       <c r="P58">
-        <v>1.6917310592</v>
+        <v>1.6820405424</v>
       </c>
       <c r="Q58">
-        <v>1.9317310592</v>
+        <v>1.9220405424</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1584336037497703</v>
+        <v>0.1607334344586703</v>
       </c>
       <c r="T58">
-        <v>1.899164371090161</v>
+        <v>1.937942820828709</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.117427462692184</v>
+        <v>4.045191893171269</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09415433681722822</v>
+        <v>0.09554100798455753</v>
       </c>
       <c r="C59">
-        <v>11.05848544209662</v>
+        <v>10.56129543755569</v>
       </c>
       <c r="D59">
-        <v>19.23268544209662</v>
+        <v>18.95609543755569</v>
       </c>
       <c r="E59">
-        <v>11.1142</v>
+        <v>11.3348</v>
       </c>
       <c r="F59">
-        <v>12.5742</v>
+        <v>12.7948</v>
       </c>
       <c r="G59">
         <v>4.4</v>
@@ -6238,45 +6238,45 @@
         <v>2.94</v>
       </c>
       <c r="M59">
-        <v>0.7267887600000003</v>
+        <v>0.7843212400000001</v>
       </c>
       <c r="N59">
-        <v>2.21321124</v>
+        <v>2.15567876</v>
       </c>
       <c r="O59">
-        <v>0.5311706975999999</v>
+        <v>0.5173629023999999</v>
       </c>
       <c r="P59">
-        <v>1.6820405424</v>
+        <v>1.6383158576</v>
       </c>
       <c r="Q59">
-        <v>1.9220405424</v>
+        <v>1.8783158576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1607334344586703</v>
+        <v>0.1631427809156132</v>
       </c>
       <c r="T59">
-        <v>1.937942820828709</v>
+        <v>1.978567863411949</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.045191893171269</v>
+        <v>3.748464085965592</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09554100798455754</v>
+        <v>0.09541147915188684</v>
       </c>
       <c r="C60">
-        <v>10.56129543755569</v>
+        <v>10.3661943822922</v>
       </c>
       <c r="D60">
-        <v>18.95609543755569</v>
+        <v>18.9815943822922</v>
       </c>
       <c r="E60">
-        <v>11.3348</v>
+        <v>11.5554</v>
       </c>
       <c r="F60">
-        <v>12.7948</v>
+        <v>13.0154</v>
       </c>
       <c r="G60">
         <v>4.4</v>
@@ -6320,28 +6320,28 @@
         <v>2.94</v>
       </c>
       <c r="M60">
-        <v>0.78432124</v>
+        <v>0.7978440200000001</v>
       </c>
       <c r="N60">
-        <v>2.15567876</v>
+        <v>2.14215598</v>
       </c>
       <c r="O60">
-        <v>0.5173629023999999</v>
+        <v>0.5141174352</v>
       </c>
       <c r="P60">
-        <v>1.6383158576</v>
+        <v>1.6280385448</v>
       </c>
       <c r="Q60">
-        <v>1.8783158576</v>
+        <v>1.8680385448</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1631427809156132</v>
+        <v>0.1656696564680167</v>
       </c>
       <c r="T60">
-        <v>1.978567863411949</v>
+        <v>2.021174615389493</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.748464085965592</v>
+        <v>3.684930796372955</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09541147915188684</v>
+        <v>0.09528195031921613</v>
       </c>
       <c r="C61">
-        <v>10.3661943822922</v>
+        <v>10.17116201965367</v>
       </c>
       <c r="D61">
-        <v>18.9815943822922</v>
+        <v>19.00716201965368</v>
       </c>
       <c r="E61">
-        <v>11.5554</v>
+        <v>11.776</v>
       </c>
       <c r="F61">
-        <v>13.0154</v>
+        <v>13.236</v>
       </c>
       <c r="G61">
         <v>4.4</v>
@@ -6402,28 +6402,28 @@
         <v>2.94</v>
       </c>
       <c r="M61">
-        <v>0.7978440200000001</v>
+        <v>0.8113668000000001</v>
       </c>
       <c r="N61">
-        <v>2.14215598</v>
+        <v>2.1286332</v>
       </c>
       <c r="O61">
-        <v>0.5141174352</v>
+        <v>0.510871968</v>
       </c>
       <c r="P61">
-        <v>1.6280385448</v>
+        <v>1.617761232</v>
       </c>
       <c r="Q61">
-        <v>1.8680385448</v>
+        <v>1.857761232</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1656696564680167</v>
+        <v>0.1683228757980403</v>
       </c>
       <c r="T61">
-        <v>2.021174615389493</v>
+        <v>2.065911704965914</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.684930796372955</v>
+        <v>3.623515283100072</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09528195031921613</v>
+        <v>0.09515242148654544</v>
       </c>
       <c r="C62">
-        <v>10.17116201965367</v>
+        <v>9.976198627595224</v>
       </c>
       <c r="D62">
-        <v>19.00716201965368</v>
+        <v>19.03279862759522</v>
       </c>
       <c r="E62">
-        <v>11.776</v>
+        <v>11.9966</v>
       </c>
       <c r="F62">
-        <v>13.236</v>
+        <v>13.4566</v>
       </c>
       <c r="G62">
         <v>4.4</v>
@@ -6484,28 +6484,28 @@
         <v>2.94</v>
       </c>
       <c r="M62">
-        <v>0.8113668000000001</v>
+        <v>0.8248895800000001</v>
       </c>
       <c r="N62">
-        <v>2.1286332</v>
+        <v>2.11511042</v>
       </c>
       <c r="O62">
-        <v>0.510871968</v>
+        <v>0.5076265007999999</v>
       </c>
       <c r="P62">
-        <v>1.617761232</v>
+        <v>1.6074839192</v>
       </c>
       <c r="Q62">
-        <v>1.857761232</v>
+        <v>1.8474839192</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1683228757980403</v>
+        <v>0.1711121576578088</v>
       </c>
       <c r="T62">
-        <v>2.065911704965914</v>
+        <v>2.112943004264204</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.623515283100072</v>
+        <v>3.564113393213185</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09515242148654544</v>
+        <v>0.09502289265387473</v>
       </c>
       <c r="C63">
-        <v>9.976198627595224</v>
+        <v>9.781304485573591</v>
       </c>
       <c r="D63">
-        <v>19.03279862759522</v>
+        <v>19.05850448557359</v>
       </c>
       <c r="E63">
-        <v>11.9966</v>
+        <v>12.2172</v>
       </c>
       <c r="F63">
-        <v>13.4566</v>
+        <v>13.6772</v>
       </c>
       <c r="G63">
         <v>4.4</v>
@@ -6566,28 +6566,28 @@
         <v>2.94</v>
       </c>
       <c r="M63">
-        <v>0.8248895800000001</v>
+        <v>0.8384123600000001</v>
       </c>
       <c r="N63">
-        <v>2.11511042</v>
+        <v>2.10158764</v>
       </c>
       <c r="O63">
-        <v>0.5076265007999999</v>
+        <v>0.5043810336</v>
       </c>
       <c r="P63">
-        <v>1.6074839192</v>
+        <v>1.5972066064</v>
       </c>
       <c r="Q63">
-        <v>1.8474839192</v>
+        <v>1.8372066064</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1711121576578088</v>
+        <v>0.1740482438259862</v>
       </c>
       <c r="T63">
-        <v>2.112943004264204</v>
+        <v>2.162449635104509</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.564113393213185</v>
+        <v>3.506627693322651</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09502289265387473</v>
+        <v>0.09623400382120403</v>
       </c>
       <c r="C64">
-        <v>9.781304485573591</v>
+        <v>9.323028261127094</v>
       </c>
       <c r="D64">
-        <v>19.05850448557359</v>
+        <v>18.8208282611271</v>
       </c>
       <c r="E64">
-        <v>12.2172</v>
+        <v>12.4378</v>
       </c>
       <c r="F64">
-        <v>13.6772</v>
+        <v>13.8978</v>
       </c>
       <c r="G64">
         <v>4.4</v>
@@ -6648,45 +6648,45 @@
         <v>2.94</v>
       </c>
       <c r="M64">
-        <v>0.8384123600000001</v>
+        <v>0.8908489800000002</v>
       </c>
       <c r="N64">
-        <v>2.10158764</v>
+        <v>2.04915102</v>
       </c>
       <c r="O64">
-        <v>0.5043810336</v>
+        <v>0.4917962447999999</v>
       </c>
       <c r="P64">
-        <v>1.5972066064</v>
+        <v>1.5573547752</v>
       </c>
       <c r="Q64">
-        <v>1.8372066064</v>
+        <v>1.7973547752</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1740482438259862</v>
+        <v>0.1771430373546055</v>
       </c>
       <c r="T64">
-        <v>2.162449635104509</v>
+        <v>2.214632300044289</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.506627693322651</v>
+        <v>3.300222670738198</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09623400382120403</v>
+        <v>0.09612575498853335</v>
       </c>
       <c r="C65">
-        <v>9.323028261127094</v>
+        <v>9.123430191764392</v>
       </c>
       <c r="D65">
-        <v>18.8208282611271</v>
+        <v>18.84183019176439</v>
       </c>
       <c r="E65">
-        <v>12.4378</v>
+        <v>12.6584</v>
       </c>
       <c r="F65">
-        <v>13.8978</v>
+        <v>14.1184</v>
       </c>
       <c r="G65">
         <v>4.4</v>
@@ -6730,28 +6730,28 @@
         <v>2.94</v>
       </c>
       <c r="M65">
-        <v>0.8908489800000002</v>
+        <v>0.9049894400000001</v>
       </c>
       <c r="N65">
-        <v>2.04915102</v>
+        <v>2.03501056</v>
       </c>
       <c r="O65">
-        <v>0.4917962447999999</v>
+        <v>0.4884025344</v>
       </c>
       <c r="P65">
-        <v>1.5573547752</v>
+        <v>1.5466080256</v>
       </c>
       <c r="Q65">
-        <v>1.7973547752</v>
+        <v>1.7866080256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1771430373546055</v>
+        <v>0.1804097638570371</v>
       </c>
       <c r="T65">
-        <v>2.214632300044289</v>
+        <v>2.269714001925169</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.300222670738198</v>
+        <v>3.248656691507914</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09612575498853335</v>
+        <v>0.09601750615586266</v>
       </c>
       <c r="C66">
-        <v>9.123430191764392</v>
+        <v>8.923879046355434</v>
       </c>
       <c r="D66">
-        <v>18.84183019176439</v>
+        <v>18.86287904635543</v>
       </c>
       <c r="E66">
-        <v>12.6584</v>
+        <v>12.879</v>
       </c>
       <c r="F66">
-        <v>14.1184</v>
+        <v>14.339</v>
       </c>
       <c r="G66">
         <v>4.4</v>
@@ -6812,28 +6812,28 @@
         <v>2.94</v>
       </c>
       <c r="M66">
-        <v>0.9049894400000001</v>
+        <v>0.9191299000000002</v>
       </c>
       <c r="N66">
-        <v>2.03501056</v>
+        <v>2.0208701</v>
       </c>
       <c r="O66">
-        <v>0.4884025344</v>
+        <v>0.4850088239999999</v>
       </c>
       <c r="P66">
-        <v>1.5466080256</v>
+        <v>1.535861276</v>
       </c>
       <c r="Q66">
-        <v>1.7866080256</v>
+        <v>1.775861276</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1804097638570371</v>
+        <v>0.1838631604453219</v>
       </c>
       <c r="T66">
-        <v>2.269714001925169</v>
+        <v>2.327943229627814</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.248656691507914</v>
+        <v>3.198677357792407</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09601750615586266</v>
+        <v>0.09590925732319194</v>
       </c>
       <c r="C67">
-        <v>8.923879046355434</v>
+        <v>8.724374982337162</v>
       </c>
       <c r="D67">
-        <v>18.86287904635543</v>
+        <v>18.88397498233716</v>
       </c>
       <c r="E67">
-        <v>12.879</v>
+        <v>13.0996</v>
       </c>
       <c r="F67">
-        <v>14.339</v>
+        <v>14.5596</v>
       </c>
       <c r="G67">
         <v>4.4</v>
@@ -6894,28 +6894,28 @@
         <v>2.94</v>
       </c>
       <c r="M67">
-        <v>0.9191299000000002</v>
+        <v>0.9332703600000002</v>
       </c>
       <c r="N67">
-        <v>2.0208701</v>
+        <v>2.00672964</v>
       </c>
       <c r="O67">
-        <v>0.4850088239999999</v>
+        <v>0.4816151135999999</v>
       </c>
       <c r="P67">
-        <v>1.535861276</v>
+        <v>1.5251145264</v>
       </c>
       <c r="Q67">
-        <v>1.775861276</v>
+        <v>1.7651145264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1838631604453219</v>
+        <v>0.1875196980093881</v>
       </c>
       <c r="T67">
-        <v>2.327943229627814</v>
+        <v>2.389597706018848</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.198677357792407</v>
+        <v>3.150212549341007</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09590925732319194</v>
+        <v>0.09580100849052123</v>
       </c>
       <c r="C68">
-        <v>8.724374982337162</v>
+        <v>8.524918157851614</v>
       </c>
       <c r="D68">
-        <v>18.88397498233716</v>
+        <v>18.90511815785162</v>
       </c>
       <c r="E68">
-        <v>13.0996</v>
+        <v>13.3202</v>
       </c>
       <c r="F68">
-        <v>14.5596</v>
+        <v>14.7802</v>
       </c>
       <c r="G68">
         <v>4.4</v>
@@ -6976,28 +6976,28 @@
         <v>2.94</v>
       </c>
       <c r="M68">
-        <v>0.9332703600000002</v>
+        <v>0.9474108200000002</v>
       </c>
       <c r="N68">
-        <v>2.00672964</v>
+        <v>1.99258918</v>
       </c>
       <c r="O68">
-        <v>0.4816151135999999</v>
+        <v>0.4782214031999999</v>
       </c>
       <c r="P68">
-        <v>1.5251145264</v>
+        <v>1.5143677768</v>
       </c>
       <c r="Q68">
-        <v>1.7651145264</v>
+        <v>1.7543677768</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1875196980093881</v>
+        <v>0.1913978439106704</v>
       </c>
       <c r="T68">
-        <v>2.389597706018848</v>
+        <v>2.454988817342673</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.150212549341007</v>
+        <v>3.103194451589649</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09580100849052123</v>
+        <v>0.09569275965785054</v>
       </c>
       <c r="C69">
-        <v>8.524918157851614</v>
+        <v>8.325508731749879</v>
       </c>
       <c r="D69">
-        <v>18.90511815785162</v>
+        <v>18.92630873174988</v>
       </c>
       <c r="E69">
-        <v>13.3202</v>
+        <v>13.5408</v>
       </c>
       <c r="F69">
-        <v>14.7802</v>
+        <v>15.0008</v>
       </c>
       <c r="G69">
         <v>4.4</v>
@@ -7058,28 +7058,28 @@
         <v>2.94</v>
       </c>
       <c r="M69">
-        <v>0.9474108200000002</v>
+        <v>0.9615512800000002</v>
       </c>
       <c r="N69">
-        <v>1.99258918</v>
+        <v>1.97844872</v>
       </c>
       <c r="O69">
-        <v>0.4782214031999999</v>
+        <v>0.4748276927999999</v>
       </c>
       <c r="P69">
-        <v>1.5143677768</v>
+        <v>1.5036210272</v>
       </c>
       <c r="Q69">
-        <v>1.7543677768</v>
+        <v>1.7436210272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1913978439106704</v>
+        <v>0.1955183739307829</v>
       </c>
       <c r="T69">
-        <v>2.454988817342673</v>
+        <v>2.524466873124237</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.103194451589649</v>
+        <v>3.057559239066272</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09569275965785054</v>
+        <v>0.09558451082517985</v>
       </c>
       <c r="C70">
-        <v>8.325508731749879</v>
+        <v>8.126146863596041</v>
       </c>
       <c r="D70">
-        <v>18.92630873174988</v>
+        <v>18.94754686359605</v>
       </c>
       <c r="E70">
-        <v>13.5408</v>
+        <v>13.7614</v>
       </c>
       <c r="F70">
-        <v>15.0008</v>
+        <v>15.2214</v>
       </c>
       <c r="G70">
         <v>4.4</v>
@@ -7140,28 +7140,28 @@
         <v>2.94</v>
       </c>
       <c r="M70">
-        <v>0.9615512800000002</v>
+        <v>0.9756917400000003</v>
       </c>
       <c r="N70">
-        <v>1.97844872</v>
+        <v>1.96430826</v>
       </c>
       <c r="O70">
-        <v>0.4748276927999999</v>
+        <v>0.4714339823999999</v>
       </c>
       <c r="P70">
-        <v>1.5036210272</v>
+        <v>1.4928742776</v>
       </c>
       <c r="Q70">
-        <v>1.7436210272</v>
+        <v>1.7328742776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1955183739307829</v>
+        <v>0.1999047445973544</v>
       </c>
       <c r="T70">
-        <v>2.524466873124237</v>
+        <v>2.598427384117515</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.057559239066272</v>
+        <v>3.01324678632618</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09558451082517985</v>
+        <v>0.09962586199250914</v>
       </c>
       <c r="C71">
-        <v>8.126146863596041</v>
+        <v>7.143672894470061</v>
       </c>
       <c r="D71">
-        <v>18.94754686359605</v>
+        <v>18.18567289447007</v>
       </c>
       <c r="E71">
-        <v>13.7614</v>
+        <v>13.982</v>
       </c>
       <c r="F71">
-        <v>15.2214</v>
+        <v>15.442</v>
       </c>
       <c r="G71">
         <v>4.4</v>
@@ -7222,45 +7222,45 @@
         <v>2.94</v>
       </c>
       <c r="M71">
-        <v>0.9756917400000003</v>
+        <v>1.1102798</v>
       </c>
       <c r="N71">
-        <v>1.96430826</v>
+        <v>1.8297202</v>
       </c>
       <c r="O71">
-        <v>0.4714339823999999</v>
+        <v>0.4391328479999999</v>
       </c>
       <c r="P71">
-        <v>1.4928742776</v>
+        <v>1.390587352</v>
       </c>
       <c r="Q71">
-        <v>1.7328742776</v>
+        <v>1.630587352</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1999047445973544</v>
+        <v>0.2045835399750305</v>
       </c>
       <c r="T71">
-        <v>2.598427384117515</v>
+        <v>2.677318595843678</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.24</v>
       </c>
       <c r="W71">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.01324678632618</v>
+        <v>2.647981166549188</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09962586199250914</v>
+        <v>0.09957689315983845</v>
       </c>
       <c r="C72">
-        <v>7.143672894470061</v>
+        <v>6.931937600335724</v>
       </c>
       <c r="D72">
-        <v>18.18567289447007</v>
+        <v>18.19453760033573</v>
       </c>
       <c r="E72">
-        <v>13.982</v>
+        <v>14.2026</v>
       </c>
       <c r="F72">
-        <v>15.442</v>
+        <v>15.6626</v>
       </c>
       <c r="G72">
         <v>4.4</v>
@@ -7304,28 +7304,28 @@
         <v>2.94</v>
       </c>
       <c r="M72">
-        <v>1.1102798</v>
+        <v>1.12614094</v>
       </c>
       <c r="N72">
-        <v>1.8297202</v>
+        <v>1.81385906</v>
       </c>
       <c r="O72">
-        <v>0.4391328479999999</v>
+        <v>0.4353261743999999</v>
       </c>
       <c r="P72">
-        <v>1.390587352</v>
+        <v>1.3785328856</v>
       </c>
       <c r="Q72">
-        <v>1.630587352</v>
+        <v>1.6185328856</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2045835399750305</v>
+        <v>0.2095850108959947</v>
       </c>
       <c r="T72">
-        <v>2.677318595843678</v>
+        <v>2.761650580792335</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.647981166549188</v>
+        <v>2.610685657161172</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09957689315983845</v>
+        <v>0.09952792432716775</v>
       </c>
       <c r="C73">
-        <v>6.931937600335726</v>
+        <v>6.720210952715044</v>
       </c>
       <c r="D73">
-        <v>18.19453760033573</v>
+        <v>18.20341095271505</v>
       </c>
       <c r="E73">
-        <v>14.2026</v>
+        <v>14.4232</v>
       </c>
       <c r="F73">
-        <v>15.6626</v>
+        <v>15.8832</v>
       </c>
       <c r="G73">
         <v>4.4</v>
@@ -7386,28 +7386,28 @@
         <v>2.94</v>
       </c>
       <c r="M73">
-        <v>1.12614094</v>
+        <v>1.14200208</v>
       </c>
       <c r="N73">
-        <v>1.81385906</v>
+        <v>1.79799792</v>
       </c>
       <c r="O73">
-        <v>0.4353261743999999</v>
+        <v>0.4315195008</v>
       </c>
       <c r="P73">
-        <v>1.3785328856</v>
+        <v>1.3664784192</v>
       </c>
       <c r="Q73">
-        <v>1.6185328856</v>
+        <v>1.6064784192</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2095850108959946</v>
+        <v>0.2149437297398848</v>
       </c>
       <c r="T73">
-        <v>2.761650580792335</v>
+        <v>2.85200627895161</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.610685657161172</v>
+        <v>2.574426134145044</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09952792432716775</v>
+        <v>0.09947895549449703</v>
       </c>
       <c r="C74">
-        <v>6.720210952715044</v>
+        <v>6.508492964264725</v>
       </c>
       <c r="D74">
-        <v>18.20341095271505</v>
+        <v>18.21229296426473</v>
       </c>
       <c r="E74">
-        <v>14.4232</v>
+        <v>14.6438</v>
       </c>
       <c r="F74">
-        <v>15.8832</v>
+        <v>16.1038</v>
       </c>
       <c r="G74">
         <v>4.4</v>
@@ -7468,28 +7468,28 @@
         <v>2.94</v>
       </c>
       <c r="M74">
-        <v>1.14200208</v>
+        <v>1.15786322</v>
       </c>
       <c r="N74">
-        <v>1.79799792</v>
+        <v>1.78213678</v>
       </c>
       <c r="O74">
-        <v>0.4315195008</v>
+        <v>0.4277128272</v>
       </c>
       <c r="P74">
-        <v>1.3664784192</v>
+        <v>1.3544239528</v>
       </c>
       <c r="Q74">
-        <v>1.6064784192</v>
+        <v>1.5944239528</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2149437297398848</v>
+        <v>0.2206993907203594</v>
       </c>
       <c r="T74">
-        <v>2.85200627895161</v>
+        <v>2.94905499178935</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.574426134145044</v>
+        <v>2.5391600227184</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09947895549449703</v>
+        <v>0.09942998666182634</v>
       </c>
       <c r="C75">
-        <v>6.508492964264725</v>
+        <v>6.296783647666192</v>
       </c>
       <c r="D75">
-        <v>18.21229296426473</v>
+        <v>18.22118364766619</v>
       </c>
       <c r="E75">
-        <v>14.6438</v>
+        <v>14.8644</v>
       </c>
       <c r="F75">
-        <v>16.1038</v>
+        <v>16.3244</v>
       </c>
       <c r="G75">
         <v>4.4</v>
@@ -7550,28 +7550,28 @@
         <v>2.94</v>
       </c>
       <c r="M75">
-        <v>1.15786322</v>
+        <v>1.17372436</v>
       </c>
       <c r="N75">
-        <v>1.78213678</v>
+        <v>1.76627564</v>
       </c>
       <c r="O75">
-        <v>0.4277128272</v>
+        <v>0.4239061535999999</v>
       </c>
       <c r="P75">
-        <v>1.3544239528</v>
+        <v>1.3423694864</v>
       </c>
       <c r="Q75">
-        <v>1.5944239528</v>
+        <v>1.5823694864</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2206993907203594</v>
+        <v>0.2268977948531782</v>
       </c>
       <c r="T75">
-        <v>2.94905499178935</v>
+        <v>3.053568990229993</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.5391600227184</v>
+        <v>2.504847049438421</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09942998666182634</v>
+        <v>0.1016040178291557</v>
       </c>
       <c r="C76">
-        <v>6.296783647666192</v>
+        <v>5.68965538560925</v>
       </c>
       <c r="D76">
-        <v>18.22118364766619</v>
+        <v>17.83465538560925</v>
       </c>
       <c r="E76">
-        <v>14.8644</v>
+        <v>15.085</v>
       </c>
       <c r="F76">
-        <v>16.3244</v>
+        <v>16.545</v>
       </c>
       <c r="G76">
         <v>4.4</v>
@@ -7632,45 +7632,45 @@
         <v>2.94</v>
       </c>
       <c r="M76">
-        <v>1.17372436</v>
+        <v>1.254111</v>
       </c>
       <c r="N76">
-        <v>1.76627564</v>
+        <v>1.685889</v>
       </c>
       <c r="O76">
-        <v>0.4239061535999999</v>
+        <v>0.4046133599999999</v>
       </c>
       <c r="P76">
-        <v>1.3423694864</v>
+        <v>1.28127564</v>
       </c>
       <c r="Q76">
-        <v>1.5823694864</v>
+        <v>1.52127564</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2268977948531782</v>
+        <v>0.2335920713166226</v>
       </c>
       <c r="T76">
-        <v>3.053568990229993</v>
+        <v>3.166444108545888</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.24</v>
       </c>
       <c r="W76">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.504847049438421</v>
+        <v>2.344290098723318</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1016040178291557</v>
+        <v>0.101584688996485</v>
       </c>
       <c r="C77">
-        <v>5.68965538560925</v>
+        <v>5.472419658122977</v>
       </c>
       <c r="D77">
-        <v>17.83465538560925</v>
+        <v>17.83801965812298</v>
       </c>
       <c r="E77">
-        <v>15.085</v>
+        <v>15.3056</v>
       </c>
       <c r="F77">
-        <v>16.545</v>
+        <v>16.7656</v>
       </c>
       <c r="G77">
         <v>4.4</v>
@@ -7714,28 +7714,28 @@
         <v>2.94</v>
       </c>
       <c r="M77">
-        <v>1.254111</v>
+        <v>1.27083248</v>
       </c>
       <c r="N77">
-        <v>1.685889</v>
+        <v>1.66916752</v>
       </c>
       <c r="O77">
-        <v>0.4046133599999999</v>
+        <v>0.4006002047999999</v>
       </c>
       <c r="P77">
-        <v>1.28127564</v>
+        <v>1.2685673152</v>
       </c>
       <c r="Q77">
-        <v>1.52127564</v>
+        <v>1.5085673152</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2335920713166226</v>
+        <v>0.2408442041520206</v>
       </c>
       <c r="T77">
-        <v>3.166444108545888</v>
+        <v>3.28872548672144</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.344290098723318</v>
+        <v>2.313444176371696</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.101584688996485</v>
+        <v>0.1015653601638142</v>
       </c>
       <c r="C78">
-        <v>5.472419658122977</v>
+        <v>5.25518520012745</v>
       </c>
       <c r="D78">
-        <v>17.83801965812298</v>
+        <v>17.84138520012745</v>
       </c>
       <c r="E78">
-        <v>15.3056</v>
+        <v>15.5262</v>
       </c>
       <c r="F78">
-        <v>16.7656</v>
+        <v>16.9862</v>
       </c>
       <c r="G78">
         <v>4.4</v>
@@ -7796,28 +7796,28 @@
         <v>2.94</v>
       </c>
       <c r="M78">
-        <v>1.27083248</v>
+        <v>1.28755396</v>
       </c>
       <c r="N78">
-        <v>1.66916752</v>
+        <v>1.65244604</v>
       </c>
       <c r="O78">
-        <v>0.4006002047999999</v>
+        <v>0.3965870495999999</v>
       </c>
       <c r="P78">
-        <v>1.2685673152</v>
+        <v>1.2558589904</v>
       </c>
       <c r="Q78">
-        <v>1.5085673152</v>
+        <v>1.4958589904</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2408442041520206</v>
+        <v>0.248726957233975</v>
       </c>
       <c r="T78">
-        <v>3.28872548672144</v>
+        <v>3.421640028216606</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.313444176371696</v>
+        <v>2.283399446808427</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1015653601638142</v>
+        <v>0.1015460313311435</v>
       </c>
       <c r="C79">
-        <v>5.25518520012745</v>
+        <v>5.037952012341371</v>
       </c>
       <c r="D79">
-        <v>17.84138520012745</v>
+        <v>17.84475201234137</v>
       </c>
       <c r="E79">
-        <v>15.5262</v>
+        <v>15.7468</v>
       </c>
       <c r="F79">
-        <v>16.9862</v>
+        <v>17.2068</v>
       </c>
       <c r="G79">
         <v>4.4</v>
@@ -7878,28 +7878,28 @@
         <v>2.94</v>
       </c>
       <c r="M79">
-        <v>1.28755396</v>
+        <v>1.30427544</v>
       </c>
       <c r="N79">
-        <v>1.65244604</v>
+        <v>1.63572456</v>
       </c>
       <c r="O79">
-        <v>0.3965870495999999</v>
+        <v>0.3925738943999999</v>
       </c>
       <c r="P79">
-        <v>1.2558589904</v>
+        <v>1.2431506656</v>
       </c>
       <c r="Q79">
-        <v>1.4958589904</v>
+        <v>1.4831506656</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.248726957233975</v>
+        <v>0.2573263242324706</v>
       </c>
       <c r="T79">
-        <v>3.421640028216606</v>
+        <v>3.566637709847697</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.283399446808427</v>
+        <v>2.254125094926267</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1015460313311435</v>
+        <v>0.1015267024984728</v>
       </c>
       <c r="C80">
-        <v>5.037952012341371</v>
+        <v>4.820720095483953</v>
       </c>
       <c r="D80">
-        <v>17.84475201234137</v>
+        <v>17.84812009548396</v>
       </c>
       <c r="E80">
-        <v>15.7468</v>
+        <v>15.9674</v>
       </c>
       <c r="F80">
-        <v>17.2068</v>
+        <v>17.4274</v>
       </c>
       <c r="G80">
         <v>4.4</v>
@@ -7960,28 +7960,28 @@
         <v>2.94</v>
       </c>
       <c r="M80">
-        <v>1.30427544</v>
+        <v>1.32099692</v>
       </c>
       <c r="N80">
-        <v>1.63572456</v>
+        <v>1.61900308</v>
       </c>
       <c r="O80">
-        <v>0.3925738943999999</v>
+        <v>0.3885607391999999</v>
       </c>
       <c r="P80">
-        <v>1.2431506656</v>
+        <v>1.2304423408</v>
       </c>
       <c r="Q80">
-        <v>1.4831506656</v>
+        <v>1.4704423408</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2573263242324706</v>
+        <v>0.2667446785641564</v>
       </c>
       <c r="T80">
-        <v>3.566637709847697</v>
+        <v>3.725444694491272</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.254125094926267</v>
+        <v>2.225591865876568</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1015267024984728</v>
+        <v>0.1015073736658021</v>
       </c>
       <c r="C81">
-        <v>4.820720095483953</v>
+        <v>4.603489450274978</v>
       </c>
       <c r="D81">
-        <v>17.84812009548396</v>
+        <v>17.85148945027498</v>
       </c>
       <c r="E81">
-        <v>15.9674</v>
+        <v>16.188</v>
       </c>
       <c r="F81">
-        <v>17.4274</v>
+        <v>17.648</v>
       </c>
       <c r="G81">
         <v>4.4</v>
@@ -8042,28 +8042,28 @@
         <v>2.94</v>
       </c>
       <c r="M81">
-        <v>1.32099692</v>
+        <v>1.3377184</v>
       </c>
       <c r="N81">
-        <v>1.61900308</v>
+        <v>1.6022816</v>
       </c>
       <c r="O81">
-        <v>0.3885607391999999</v>
+        <v>0.3845475839999999</v>
       </c>
       <c r="P81">
-        <v>1.2304423408</v>
+        <v>1.217734016</v>
       </c>
       <c r="Q81">
-        <v>1.4704423408</v>
+        <v>1.457734016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2667446785641564</v>
+        <v>0.2771048683290108</v>
       </c>
       <c r="T81">
-        <v>3.725444694491272</v>
+        <v>3.900132377599204</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.225591865876568</v>
+        <v>2.197771967553111</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1015073736658021</v>
+        <v>0.1014880448331315</v>
       </c>
       <c r="C82">
-        <v>4.603489450274978</v>
+        <v>4.386260077434766</v>
       </c>
       <c r="D82">
-        <v>17.85148945027498</v>
+        <v>17.85486007743477</v>
       </c>
       <c r="E82">
-        <v>16.188</v>
+        <v>16.4086</v>
       </c>
       <c r="F82">
-        <v>17.648</v>
+        <v>17.8686</v>
       </c>
       <c r="G82">
         <v>4.4</v>
@@ -8124,28 +8124,28 @@
         <v>2.94</v>
       </c>
       <c r="M82">
-        <v>1.3377184</v>
+        <v>1.35443988</v>
       </c>
       <c r="N82">
-        <v>1.6022816</v>
+        <v>1.58556012</v>
       </c>
       <c r="O82">
-        <v>0.3845475839999999</v>
+        <v>0.3805344287999999</v>
       </c>
       <c r="P82">
-        <v>1.217734016</v>
+        <v>1.2050256912</v>
       </c>
       <c r="Q82">
-        <v>1.457734016</v>
+        <v>1.4450256912</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2771048683290108</v>
+        <v>0.2885556043849024</v>
       </c>
       <c r="T82">
-        <v>3.900132377599204</v>
+        <v>4.093208237876393</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.197771967553111</v>
+        <v>2.170638980299369</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1014880448331315</v>
+        <v>0.1014687160004607</v>
       </c>
       <c r="C83">
-        <v>4.386260077434766</v>
+        <v>4.169031977684181</v>
       </c>
       <c r="D83">
-        <v>17.85486007743477</v>
+        <v>17.85823197768418</v>
       </c>
       <c r="E83">
-        <v>16.4086</v>
+        <v>16.6292</v>
       </c>
       <c r="F83">
-        <v>17.8686</v>
+        <v>18.0892</v>
       </c>
       <c r="G83">
         <v>4.4</v>
@@ -8206,28 +8206,28 @@
         <v>2.94</v>
       </c>
       <c r="M83">
-        <v>1.35443988</v>
+        <v>1.37116136</v>
       </c>
       <c r="N83">
-        <v>1.58556012</v>
+        <v>1.56883864</v>
       </c>
       <c r="O83">
-        <v>0.3805344287999999</v>
+        <v>0.3765212735999999</v>
       </c>
       <c r="P83">
-        <v>1.2050256912</v>
+        <v>1.1923173664</v>
       </c>
       <c r="Q83">
-        <v>1.4450256912</v>
+        <v>1.4323173664</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2885556043849024</v>
+        <v>0.3012786444470042</v>
       </c>
       <c r="T83">
-        <v>4.093208237876393</v>
+        <v>4.307736971517713</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.170638980299369</v>
+        <v>2.144167773222547</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1014687160004607</v>
+        <v>0.1014493871677901</v>
       </c>
       <c r="C84">
-        <v>4.169031977684181</v>
+        <v>3.95180515174463</v>
       </c>
       <c r="D84">
-        <v>17.85823197768418</v>
+        <v>17.86160515174463</v>
       </c>
       <c r="E84">
-        <v>16.6292</v>
+        <v>16.8498</v>
       </c>
       <c r="F84">
-        <v>18.0892</v>
+        <v>18.3098</v>
       </c>
       <c r="G84">
         <v>4.4</v>
@@ -8288,28 +8288,28 @@
         <v>2.94</v>
       </c>
       <c r="M84">
-        <v>1.37116136</v>
+        <v>1.38788284</v>
       </c>
       <c r="N84">
-        <v>1.56883864</v>
+        <v>1.55211716</v>
       </c>
       <c r="O84">
-        <v>0.3765212735999999</v>
+        <v>0.3725081183999999</v>
       </c>
       <c r="P84">
-        <v>1.1923173664</v>
+        <v>1.1796090416</v>
       </c>
       <c r="Q84">
-        <v>1.4323173664</v>
+        <v>1.4196090416</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3012786444470042</v>
+        <v>0.3154985127517063</v>
       </c>
       <c r="T84">
-        <v>4.307736971517713</v>
+        <v>4.547504379705072</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.144167773222547</v>
+        <v>2.118334426557215</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1014493871677901</v>
+        <v>0.1014300583351194</v>
       </c>
       <c r="C85">
-        <v>3.95180515174463</v>
+        <v>3.734579600338055</v>
       </c>
       <c r="D85">
-        <v>17.86160515174463</v>
+        <v>17.86497960033806</v>
       </c>
       <c r="E85">
-        <v>16.8498</v>
+        <v>17.0704</v>
       </c>
       <c r="F85">
-        <v>18.3098</v>
+        <v>18.5304</v>
       </c>
       <c r="G85">
         <v>4.4</v>
@@ -8370,28 +8370,28 @@
         <v>2.94</v>
       </c>
       <c r="M85">
-        <v>1.38788284</v>
+        <v>1.40460432</v>
       </c>
       <c r="N85">
-        <v>1.55211716</v>
+        <v>1.535395679999999</v>
       </c>
       <c r="O85">
-        <v>0.3725081183999999</v>
+        <v>0.3684949631999999</v>
       </c>
       <c r="P85">
-        <v>1.1796090416</v>
+        <v>1.1669007168</v>
       </c>
       <c r="Q85">
-        <v>1.4196090416</v>
+        <v>1.4069007168</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3154985127517063</v>
+        <v>0.3314958645944961</v>
       </c>
       <c r="T85">
-        <v>4.547504379705072</v>
+        <v>4.81724271391585</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.118334426557215</v>
+        <v>2.093116159574391</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1014300583351194</v>
+        <v>0.1014107295024487</v>
       </c>
       <c r="C86">
-        <v>3.734579600338066</v>
+        <v>3.517355324186976</v>
       </c>
       <c r="D86">
-        <v>17.86497960033806</v>
+        <v>17.86835532418698</v>
       </c>
       <c r="E86">
-        <v>17.0704</v>
+        <v>17.291</v>
       </c>
       <c r="F86">
-        <v>18.5304</v>
+        <v>18.751</v>
       </c>
       <c r="G86">
         <v>4.4</v>
@@ -8452,28 +8452,28 @@
         <v>2.94</v>
       </c>
       <c r="M86">
-        <v>1.40460432</v>
+        <v>1.4213258</v>
       </c>
       <c r="N86">
-        <v>1.53539568</v>
+        <v>1.5186742</v>
       </c>
       <c r="O86">
-        <v>0.3684949631999999</v>
+        <v>0.3644818079999999</v>
       </c>
       <c r="P86">
-        <v>1.1669007168</v>
+        <v>1.154192392</v>
       </c>
       <c r="Q86">
-        <v>1.4069007168</v>
+        <v>1.394192392</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3314958645944959</v>
+        <v>0.349626196682991</v>
       </c>
       <c r="T86">
-        <v>4.817242713915847</v>
+        <v>5.122946159354729</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.093116159574391</v>
+        <v>2.068491263579399</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1014107295024487</v>
+        <v>0.1013914006697779</v>
       </c>
       <c r="C87">
-        <v>3.517355324186976</v>
+        <v>3.30013232401442</v>
       </c>
       <c r="D87">
-        <v>17.86835532418698</v>
+        <v>17.87173232401442</v>
       </c>
       <c r="E87">
-        <v>17.291</v>
+        <v>17.5116</v>
       </c>
       <c r="F87">
-        <v>18.751</v>
+        <v>18.9716</v>
       </c>
       <c r="G87">
         <v>4.4</v>
@@ -8534,28 +8534,28 @@
         <v>2.94</v>
       </c>
       <c r="M87">
-        <v>1.4213258</v>
+        <v>1.43804728</v>
       </c>
       <c r="N87">
-        <v>1.5186742</v>
+        <v>1.50195272</v>
       </c>
       <c r="O87">
-        <v>0.3644818079999999</v>
+        <v>0.3604686527999999</v>
       </c>
       <c r="P87">
-        <v>1.154192392</v>
+        <v>1.1414840672</v>
       </c>
       <c r="Q87">
-        <v>1.394192392</v>
+        <v>1.3814840672</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.349626196682991</v>
+        <v>0.3703465762126996</v>
       </c>
       <c r="T87">
-        <v>5.122946159354729</v>
+        <v>5.472321525570593</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.068491263579399</v>
+        <v>2.044439039584289</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1013914006697779</v>
+        <v>0.1013720718371073</v>
       </c>
       <c r="C88">
-        <v>3.30013232401442</v>
+        <v>3.082910600543972</v>
       </c>
       <c r="D88">
-        <v>17.87173232401442</v>
+        <v>17.87511060054398</v>
       </c>
       <c r="E88">
-        <v>17.5116</v>
+        <v>17.7322</v>
       </c>
       <c r="F88">
-        <v>18.9716</v>
+        <v>19.1922</v>
       </c>
       <c r="G88">
         <v>4.4</v>
@@ -8616,28 +8616,28 @@
         <v>2.94</v>
       </c>
       <c r="M88">
-        <v>1.43804728</v>
+        <v>1.45476876</v>
       </c>
       <c r="N88">
-        <v>1.50195272</v>
+        <v>1.48523124</v>
       </c>
       <c r="O88">
-        <v>0.3604686527999999</v>
+        <v>0.3564554975999999</v>
       </c>
       <c r="P88">
-        <v>1.1414840672</v>
+        <v>1.1287757424</v>
       </c>
       <c r="Q88">
-        <v>1.3814840672</v>
+        <v>1.3687757424</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3703465762126996</v>
+        <v>0.3942547064392865</v>
       </c>
       <c r="T88">
-        <v>5.472321525570593</v>
+        <v>5.87544694812736</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.044439039584289</v>
+        <v>2.020939740278723</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1013720718371073</v>
+        <v>0.1108497030044366</v>
       </c>
       <c r="C89">
-        <v>3.082910600543972</v>
+        <v>1.346044753046204</v>
       </c>
       <c r="D89">
-        <v>17.87511060054398</v>
+        <v>16.3588447530462</v>
       </c>
       <c r="E89">
-        <v>17.7322</v>
+        <v>17.9528</v>
       </c>
       <c r="F89">
-        <v>19.1922</v>
+        <v>19.4128</v>
       </c>
       <c r="G89">
         <v>4.4</v>
@@ -8698,45 +8698,45 @@
         <v>2.94</v>
       </c>
       <c r="M89">
-        <v>1.45476876</v>
+        <v>1.747152</v>
       </c>
       <c r="N89">
-        <v>1.48523124</v>
+        <v>1.192848</v>
       </c>
       <c r="O89">
-        <v>0.3564554975999999</v>
+        <v>0.28628352</v>
       </c>
       <c r="P89">
-        <v>1.1287757424</v>
+        <v>0.9065644799999999</v>
       </c>
       <c r="Q89">
-        <v>1.3687757424</v>
+        <v>1.14656448</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3942547064392865</v>
+        <v>0.4221475250369713</v>
       </c>
       <c r="T89">
-        <v>5.87544694812736</v>
+        <v>6.345759941110256</v>
       </c>
       <c r="U89">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
         <v>0.24</v>
       </c>
       <c r="W89">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.020939740278723</v>
+        <v>1.682738536772988</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1108497030044366</v>
+        <v>0.1109382941717658</v>
       </c>
       <c r="C90">
-        <v>1.346044753046204</v>
+        <v>1.112484136785049</v>
       </c>
       <c r="D90">
-        <v>16.3588447530462</v>
+        <v>16.34588413678505</v>
       </c>
       <c r="E90">
-        <v>17.9528</v>
+        <v>18.1734</v>
       </c>
       <c r="F90">
-        <v>19.4128</v>
+        <v>19.6334</v>
       </c>
       <c r="G90">
         <v>4.4</v>
@@ -8780,28 +8780,28 @@
         <v>2.94</v>
       </c>
       <c r="M90">
-        <v>1.747152</v>
+        <v>1.767006</v>
       </c>
       <c r="N90">
-        <v>1.192848</v>
+        <v>1.172994</v>
       </c>
       <c r="O90">
-        <v>0.28628352</v>
+        <v>0.28151856</v>
       </c>
       <c r="P90">
-        <v>0.9065644799999999</v>
+        <v>0.8914754399999999</v>
       </c>
       <c r="Q90">
-        <v>1.14656448</v>
+        <v>1.13147544</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4221475250369713</v>
+        <v>0.4551117651978714</v>
       </c>
       <c r="T90">
-        <v>6.345759941110256</v>
+        <v>6.901584387362766</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.682738536772988</v>
+        <v>1.663831362202505</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1109382941717658</v>
+        <v>0.1110268853390952</v>
       </c>
       <c r="C91">
-        <v>1.112484136785049</v>
+        <v>0.8789440408721596</v>
       </c>
       <c r="D91">
-        <v>16.34588413678505</v>
+        <v>16.33294404087216</v>
       </c>
       <c r="E91">
-        <v>18.1734</v>
+        <v>18.394</v>
       </c>
       <c r="F91">
-        <v>19.6334</v>
+        <v>19.854</v>
       </c>
       <c r="G91">
         <v>4.4</v>
@@ -8862,28 +8862,28 @@
         <v>2.94</v>
       </c>
       <c r="M91">
-        <v>1.767006</v>
+        <v>1.78686</v>
       </c>
       <c r="N91">
-        <v>1.172994</v>
+        <v>1.15314</v>
       </c>
       <c r="O91">
-        <v>0.28151856</v>
+        <v>0.2767535999999999</v>
       </c>
       <c r="P91">
-        <v>0.8914754399999999</v>
+        <v>0.8763863999999999</v>
       </c>
       <c r="Q91">
-        <v>1.13147544</v>
+        <v>1.1163864</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4551117651978714</v>
+        <v>0.4946688533909516</v>
       </c>
       <c r="T91">
-        <v>6.901584387362766</v>
+        <v>7.568573722865782</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.663831362202505</v>
+        <v>1.645344347066922</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1110268853390952</v>
+        <v>0.1111154765064244</v>
       </c>
       <c r="C92">
-        <v>0.8789440408721596</v>
+        <v>0.645424416611732</v>
       </c>
       <c r="D92">
-        <v>16.33294404087216</v>
+        <v>16.32002441661173</v>
       </c>
       <c r="E92">
-        <v>18.394</v>
+        <v>18.6146</v>
       </c>
       <c r="F92">
-        <v>19.854</v>
+        <v>20.0746</v>
       </c>
       <c r="G92">
         <v>4.4</v>
@@ -8944,28 +8944,28 @@
         <v>2.94</v>
       </c>
       <c r="M92">
-        <v>1.78686</v>
+        <v>1.806714</v>
       </c>
       <c r="N92">
-        <v>1.15314</v>
+        <v>1.133286</v>
       </c>
       <c r="O92">
-        <v>0.2767535999999999</v>
+        <v>0.2719886399999999</v>
       </c>
       <c r="P92">
-        <v>0.8763863999999999</v>
+        <v>0.8612973599999997</v>
       </c>
       <c r="Q92">
-        <v>1.1163864</v>
+        <v>1.10129736</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4946688533909516</v>
+        <v>0.5430164056269384</v>
       </c>
       <c r="T92">
-        <v>7.568573722865782</v>
+        <v>8.3837829107028</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.645344347066922</v>
+        <v>1.627263639956296</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1111154765064244</v>
+        <v>0.1112040676737538</v>
       </c>
       <c r="C93">
-        <v>0.645424416611732</v>
+        <v>0.4119252154619346</v>
       </c>
       <c r="D93">
-        <v>16.32002441661173</v>
+        <v>16.30712521546194</v>
       </c>
       <c r="E93">
-        <v>18.6146</v>
+        <v>18.8352</v>
       </c>
       <c r="F93">
-        <v>20.0746</v>
+        <v>20.2952</v>
       </c>
       <c r="G93">
         <v>4.4</v>
@@ -9026,28 +9026,28 @@
         <v>2.94</v>
       </c>
       <c r="M93">
-        <v>1.806714</v>
+        <v>1.826568</v>
       </c>
       <c r="N93">
-        <v>1.133286</v>
+        <v>1.113432</v>
       </c>
       <c r="O93">
-        <v>0.2719886399999999</v>
+        <v>0.26722368</v>
       </c>
       <c r="P93">
-        <v>0.8612973599999997</v>
+        <v>0.84620832</v>
       </c>
       <c r="Q93">
-        <v>1.10129736</v>
+        <v>1.08620832</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5430164056269384</v>
+        <v>0.6034508459219222</v>
       </c>
       <c r="T93">
-        <v>8.3837829107028</v>
+        <v>9.402794395499075</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.627263639956296</v>
+        <v>1.609575991695902</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1112040676737538</v>
+        <v>0.1112926588410831</v>
       </c>
       <c r="C94">
-        <v>0.4119252154619346</v>
+        <v>0.1784463890342955</v>
       </c>
       <c r="D94">
-        <v>16.30712521546194</v>
+        <v>16.2942463890343</v>
       </c>
       <c r="E94">
-        <v>18.8352</v>
+        <v>19.0558</v>
       </c>
       <c r="F94">
-        <v>20.2952</v>
+        <v>20.5158</v>
       </c>
       <c r="G94">
         <v>4.4</v>
@@ -9108,28 +9108,28 @@
         <v>2.94</v>
       </c>
       <c r="M94">
-        <v>1.826568</v>
+        <v>1.846422</v>
       </c>
       <c r="N94">
-        <v>1.113432</v>
+        <v>1.093578</v>
       </c>
       <c r="O94">
-        <v>0.26722368</v>
+        <v>0.2624587199999999</v>
       </c>
       <c r="P94">
-        <v>0.84620832</v>
+        <v>0.8311192799999998</v>
       </c>
       <c r="Q94">
-        <v>1.08620832</v>
+        <v>1.07111928</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6034508459219222</v>
+        <v>0.6811522691583297</v>
       </c>
       <c r="T94">
-        <v>9.402794395499075</v>
+        <v>10.71295201880857</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.609575991695902</v>
+        <v>1.592268722967989</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1112926588410831</v>
+        <v>0.1113812500084123</v>
       </c>
       <c r="C95">
-        <v>0.1784463890342955</v>
+        <v>-0.05501211090693658</v>
       </c>
       <c r="D95">
-        <v>16.2942463890343</v>
+        <v>16.28138788909306</v>
       </c>
       <c r="E95">
-        <v>19.0558</v>
+        <v>19.2764</v>
       </c>
       <c r="F95">
-        <v>20.5158</v>
+        <v>20.7364</v>
       </c>
       <c r="G95">
         <v>4.4</v>
@@ -9190,28 +9190,28 @@
         <v>2.94</v>
       </c>
       <c r="M95">
-        <v>1.846422</v>
+        <v>1.866276</v>
       </c>
       <c r="N95">
-        <v>1.093578</v>
+        <v>1.073724</v>
       </c>
       <c r="O95">
-        <v>0.2624587199999999</v>
+        <v>0.2576937599999999</v>
       </c>
       <c r="P95">
-        <v>0.8311192799999998</v>
+        <v>0.8160302399999997</v>
       </c>
       <c r="Q95">
-        <v>1.07111928</v>
+        <v>1.05603024</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6811522691583297</v>
+        <v>0.7847541668068732</v>
       </c>
       <c r="T95">
-        <v>10.71295201880857</v>
+        <v>12.4598288498879</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.592268722967989</v>
+        <v>1.575329694000244</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1113812500084123</v>
+        <v>0.1114698411757417</v>
       </c>
       <c r="C96">
-        <v>-0.05501211090693658</v>
+        <v>-0.2884503324453753</v>
       </c>
       <c r="D96">
-        <v>16.28138788909306</v>
+        <v>16.26854966755463</v>
       </c>
       <c r="E96">
-        <v>19.2764</v>
+        <v>19.497</v>
       </c>
       <c r="F96">
-        <v>20.7364</v>
+        <v>20.957</v>
       </c>
       <c r="G96">
         <v>4.4</v>
@@ -9272,28 +9272,28 @@
         <v>2.94</v>
       </c>
       <c r="M96">
-        <v>1.866276</v>
+        <v>1.88613</v>
       </c>
       <c r="N96">
-        <v>1.073724</v>
+        <v>1.05387</v>
       </c>
       <c r="O96">
-        <v>0.2576937599999999</v>
+        <v>0.2529287999999999</v>
       </c>
       <c r="P96">
-        <v>0.8160302399999997</v>
+        <v>0.8009411999999998</v>
       </c>
       <c r="Q96">
-        <v>1.05603024</v>
+        <v>1.0409412</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7847541668068732</v>
+        <v>0.9297968235148343</v>
       </c>
       <c r="T96">
-        <v>12.4598288498879</v>
+        <v>14.90545641339896</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.575329694000244</v>
+        <v>1.558747276168662</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1114698411757417</v>
+        <v>0.111558432343071</v>
       </c>
       <c r="C97">
-        <v>-0.2884503324453753</v>
+        <v>-0.5218683235130683</v>
       </c>
       <c r="D97">
-        <v>16.26854966755463</v>
+        <v>16.25573167648693</v>
       </c>
       <c r="E97">
-        <v>19.497</v>
+        <v>19.7176</v>
       </c>
       <c r="F97">
-        <v>20.957</v>
+        <v>21.17760000000001</v>
       </c>
       <c r="G97">
         <v>4.4</v>
@@ -9354,28 +9354,28 @@
         <v>2.94</v>
       </c>
       <c r="M97">
-        <v>1.88613</v>
+        <v>1.905984</v>
       </c>
       <c r="N97">
-        <v>1.05387</v>
+        <v>1.034016</v>
       </c>
       <c r="O97">
-        <v>0.2529287999999999</v>
+        <v>0.2481638399999999</v>
       </c>
       <c r="P97">
-        <v>0.8009411999999998</v>
+        <v>0.7858521599999997</v>
       </c>
       <c r="Q97">
-        <v>1.0409412</v>
+        <v>1.02585216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9297968235148343</v>
+        <v>1.147360808576776</v>
       </c>
       <c r="T97">
-        <v>14.90545641339896</v>
+        <v>18.57389775866555</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.558747276168662</v>
+        <v>1.542510325375239</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.111558432343071</v>
+        <v>0.1116470235104003</v>
       </c>
       <c r="C98">
-        <v>-0.5218683235130648</v>
+        <v>-0.7552661318911404</v>
       </c>
       <c r="D98">
-        <v>16.25573167648693</v>
+        <v>16.24293386810886</v>
       </c>
       <c r="E98">
-        <v>19.7176</v>
+        <v>19.9382</v>
       </c>
       <c r="F98">
-        <v>21.1776</v>
+        <v>21.3982</v>
       </c>
       <c r="G98">
         <v>4.4</v>
@@ -9436,28 +9436,28 @@
         <v>2.94</v>
       </c>
       <c r="M98">
-        <v>1.905984</v>
+        <v>1.925838</v>
       </c>
       <c r="N98">
-        <v>1.034016</v>
+        <v>1.014162</v>
       </c>
       <c r="O98">
-        <v>0.2481638399999999</v>
+        <v>0.2433988799999999</v>
       </c>
       <c r="P98">
-        <v>0.7858521599999999</v>
+        <v>0.7707631199999998</v>
       </c>
       <c r="Q98">
-        <v>1.02585216</v>
+        <v>1.01076312</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.147360808576773</v>
+        <v>1.509967450346674</v>
       </c>
       <c r="T98">
-        <v>18.5738977586655</v>
+        <v>24.68796666744312</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.542510325375239</v>
+        <v>1.526608157072402</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1116470235104003</v>
+        <v>0.1117356146777296</v>
       </c>
       <c r="C99">
-        <v>-0.7552661318911404</v>
+        <v>-0.9886438052103657</v>
       </c>
       <c r="D99">
-        <v>16.24293386810886</v>
+        <v>16.23015619478963</v>
       </c>
       <c r="E99">
-        <v>19.9382</v>
+        <v>20.1588</v>
       </c>
       <c r="F99">
-        <v>21.3982</v>
+        <v>21.6188</v>
       </c>
       <c r="G99">
         <v>4.4</v>
@@ -9518,28 +9518,28 @@
         <v>2.94</v>
       </c>
       <c r="M99">
-        <v>1.925838</v>
+        <v>1.945692</v>
       </c>
       <c r="N99">
-        <v>1.014162</v>
+        <v>0.994308</v>
       </c>
       <c r="O99">
-        <v>0.2433988799999999</v>
+        <v>0.23863392</v>
       </c>
       <c r="P99">
-        <v>0.7707631199999998</v>
+        <v>0.75567408</v>
       </c>
       <c r="Q99">
-        <v>1.01076312</v>
+        <v>0.9956740800000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.509967450346674</v>
+        <v>2.235180733886475</v>
       </c>
       <c r="T99">
-        <v>24.68796666744312</v>
+        <v>36.91610448499836</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.526608157072402</v>
+        <v>1.511030522816561</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1117356146777296</v>
+        <v>0.1585834773633383</v>
       </c>
       <c r="C100">
-        <v>-0.9886438052103657</v>
+        <v>-5.977373582375316</v>
       </c>
       <c r="D100">
-        <v>16.23015619478963</v>
+        <v>11.46202641762468</v>
       </c>
       <c r="E100">
-        <v>20.1588</v>
+        <v>20.3794</v>
       </c>
       <c r="F100">
-        <v>21.6188</v>
+        <v>21.8394</v>
       </c>
       <c r="G100">
         <v>4.4</v>
@@ -9600,129 +9600,47 @@
         <v>2.94</v>
       </c>
       <c r="M100">
-        <v>1.945692</v>
+        <v>3.206023920000001</v>
       </c>
       <c r="N100">
-        <v>0.994308</v>
+        <v>-0.2660239200000007</v>
       </c>
       <c r="O100">
-        <v>0.23863392</v>
+        <v>-0.06384574080000018</v>
       </c>
       <c r="P100">
-        <v>0.75567408</v>
+        <v>-0.2021781792000006</v>
       </c>
       <c r="Q100">
-        <v>0.9956740800000002</v>
+        <v>0.03782182079999963</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.235180733886475</v>
+        <v>4.523697147031925</v>
       </c>
       <c r="T100">
-        <v>36.91610448499836</v>
+        <v>75.50377894276205</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.24</v>
+        <v>0.2200856941828431</v>
       </c>
       <c r="W100">
-        <v>0.0684</v>
+        <v>0.1144914200939586</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.511030522816561</v>
+        <v>0.9170237257618462</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1585834773633383</v>
-      </c>
-      <c r="C101">
-        <v>-5.977373582375316</v>
-      </c>
-      <c r="D101">
-        <v>11.46202641762468</v>
-      </c>
-      <c r="E101">
-        <v>20.3794</v>
-      </c>
-      <c r="F101">
-        <v>21.8394</v>
-      </c>
-      <c r="G101">
-        <v>4.4</v>
-      </c>
-      <c r="H101">
-        <v>20.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.18</v>
-      </c>
-      <c r="K101">
-        <v>0.2400000000000002</v>
-      </c>
-      <c r="L101">
-        <v>2.94</v>
-      </c>
-      <c r="M101">
-        <v>3.206023920000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.2660239200000007</v>
-      </c>
-      <c r="O101">
-        <v>-0.06384574080000018</v>
-      </c>
-      <c r="P101">
-        <v>-0.2021781792000006</v>
-      </c>
-      <c r="Q101">
-        <v>0.03782182079999963</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.523697147031925</v>
-      </c>
-      <c r="T101">
-        <v>75.50377894276205</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2200856941828431</v>
-      </c>
-      <c r="W101">
-        <v>0.1144914200939586</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9170237257618462</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
